--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P554"/>
+  <dimension ref="A1:P557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30366,6 +30366,168 @@
         <v>401.07</v>
       </c>
       <c r="P554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>367.32</v>
+      </c>
+      <c r="C555" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="D555" t="n">
+        <v>362.79</v>
+      </c>
+      <c r="E555" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="F555" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="G555" t="n">
+        <v>369.01</v>
+      </c>
+      <c r="H555" t="n">
+        <v>365.86</v>
+      </c>
+      <c r="I555" t="n">
+        <v>363.9</v>
+      </c>
+      <c r="J555" t="n">
+        <v>361.9</v>
+      </c>
+      <c r="K555" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="L555" t="n">
+        <v>366.22</v>
+      </c>
+      <c r="M555" t="n">
+        <v>364.86</v>
+      </c>
+      <c r="N555" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="O555" t="n">
+        <v>400.72</v>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="C556" t="n">
+        <v>371.67</v>
+      </c>
+      <c r="D556" t="n">
+        <v>363.73</v>
+      </c>
+      <c r="E556" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="F556" t="n">
+        <v>374.72</v>
+      </c>
+      <c r="G556" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="H556" t="n">
+        <v>366.26</v>
+      </c>
+      <c r="I556" t="n">
+        <v>364.65</v>
+      </c>
+      <c r="J556" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="K556" t="n">
+        <v>361.18</v>
+      </c>
+      <c r="L556" t="n">
+        <v>366.84</v>
+      </c>
+      <c r="M556" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="N556" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="O556" t="n">
+        <v>401.25</v>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>369.63</v>
+      </c>
+      <c r="C557" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="D557" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="E557" t="n">
+        <v>371.04</v>
+      </c>
+      <c r="F557" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="G557" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="H557" t="n">
+        <v>365.42</v>
+      </c>
+      <c r="I557" t="n">
+        <v>364.14</v>
+      </c>
+      <c r="J557" t="n">
+        <v>362.33</v>
+      </c>
+      <c r="K557" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="L557" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="M557" t="n">
+        <v>364.76</v>
+      </c>
+      <c r="N557" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="O557" t="n">
+        <v>400.65</v>
+      </c>
+      <c r="P557" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30382,7 +30544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B626"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36645,6 +36807,36 @@
       </c>
       <c r="B626" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
@@ -36813,28 +37005,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2775810736777711</v>
+        <v>0.2766300775670157</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1055438264515396</v>
+        <v>0.1060395404686491</v>
       </c>
       <c r="M2" t="n">
-        <v>4.565826832946724</v>
+        <v>4.547210253391558</v>
       </c>
       <c r="N2" t="n">
-        <v>36.64102205933448</v>
+        <v>36.45321955290803</v>
       </c>
       <c r="O2" t="n">
-        <v>6.053182804057258</v>
+        <v>6.037650168145554</v>
       </c>
       <c r="P2" t="n">
-        <v>361.7270917150632</v>
+        <v>361.7366593872245</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36891,28 +37083,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1946514703686953</v>
+        <v>0.1908786817693856</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K3" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1094680586125696</v>
+        <v>0.1065184790675167</v>
       </c>
       <c r="M3" t="n">
-        <v>3.308840679791602</v>
+        <v>3.311442581716419</v>
       </c>
       <c r="N3" t="n">
-        <v>17.32573022637095</v>
+        <v>17.29848286140666</v>
       </c>
       <c r="O3" t="n">
-        <v>4.162418795168375</v>
+        <v>4.159144486719193</v>
       </c>
       <c r="P3" t="n">
-        <v>369.8988122684846</v>
+        <v>369.9367597534207</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36969,28 +37161,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1968826260957701</v>
+        <v>0.1888046126246037</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08145517268487812</v>
+        <v>0.07542125385895315</v>
       </c>
       <c r="M4" t="n">
-        <v>3.912374823237796</v>
+        <v>3.934049142740071</v>
       </c>
       <c r="N4" t="n">
-        <v>24.52777311810628</v>
+        <v>24.69232470047101</v>
       </c>
       <c r="O4" t="n">
-        <v>4.952552182269893</v>
+        <v>4.969137218921511</v>
       </c>
       <c r="P4" t="n">
-        <v>365.5210392177496</v>
+        <v>365.6023503398782</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37047,28 +37239,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2232763044434704</v>
+        <v>0.2184073857304746</v>
       </c>
       <c r="J5" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K5" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09219415029172706</v>
+        <v>0.08925195657897678</v>
       </c>
       <c r="M5" t="n">
-        <v>4.391595217095918</v>
+        <v>4.391634611089477</v>
       </c>
       <c r="N5" t="n">
-        <v>27.54460366227276</v>
+        <v>27.5043739236372</v>
       </c>
       <c r="O5" t="n">
-        <v>5.248295310124304</v>
+        <v>5.244461261525077</v>
       </c>
       <c r="P5" t="n">
-        <v>370.0749846752159</v>
+        <v>370.1239952106598</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37125,28 +37317,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2204764740910672</v>
+        <v>0.2134535556108815</v>
       </c>
       <c r="J6" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K6" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1028823531557569</v>
+        <v>0.09731563782249941</v>
       </c>
       <c r="M6" t="n">
-        <v>3.761327484252426</v>
+        <v>3.77500317841543</v>
       </c>
       <c r="N6" t="n">
-        <v>23.78453508134256</v>
+        <v>23.88068024892628</v>
       </c>
       <c r="O6" t="n">
-        <v>4.876939109866204</v>
+        <v>4.886786290490538</v>
       </c>
       <c r="P6" t="n">
-        <v>375.0151166657795</v>
+        <v>375.085809033248</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37203,28 +37395,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3297093057229528</v>
+        <v>0.3213400906349935</v>
       </c>
       <c r="J7" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K7" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2204777838945495</v>
+        <v>0.211373530255428</v>
       </c>
       <c r="M7" t="n">
-        <v>3.48814386348144</v>
+        <v>3.50876233637313</v>
       </c>
       <c r="N7" t="n">
-        <v>21.56689966150218</v>
+        <v>21.76893556283668</v>
       </c>
       <c r="O7" t="n">
-        <v>4.644017620714006</v>
+        <v>4.665719190311037</v>
       </c>
       <c r="P7" t="n">
-        <v>368.2621955951925</v>
+        <v>368.3464386755548</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37281,28 +37473,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2618729113882376</v>
+        <v>0.2588261869855971</v>
       </c>
       <c r="J8" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K8" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1540228206389915</v>
+        <v>0.1523285341359235</v>
       </c>
       <c r="M8" t="n">
-        <v>3.644984732907968</v>
+        <v>3.638777916854956</v>
       </c>
       <c r="N8" t="n">
-        <v>21.13568728653205</v>
+        <v>21.0644125223758</v>
       </c>
       <c r="O8" t="n">
-        <v>4.597356554209392</v>
+        <v>4.589598296406321</v>
       </c>
       <c r="P8" t="n">
-        <v>361.7589168588196</v>
+        <v>361.7895857260176</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37359,28 +37551,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3181727252046398</v>
+        <v>0.3125921826086395</v>
       </c>
       <c r="J9" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K9" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2199940196358663</v>
+        <v>0.2148775414242455</v>
       </c>
       <c r="M9" t="n">
-        <v>3.568987235699056</v>
+        <v>3.574041424009888</v>
       </c>
       <c r="N9" t="n">
-        <v>20.14070178803261</v>
+        <v>20.17387015521508</v>
       </c>
       <c r="O9" t="n">
-        <v>4.487839322884968</v>
+        <v>4.491533163098663</v>
       </c>
       <c r="P9" t="n">
-        <v>361.0003546562989</v>
+        <v>361.056527104756</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37437,28 +37629,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3306792180451332</v>
+        <v>0.324474812811705</v>
       </c>
       <c r="J10" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K10" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2234845886177671</v>
+        <v>0.2176839805019983</v>
       </c>
       <c r="M10" t="n">
-        <v>3.434825320430987</v>
+        <v>3.446475027597873</v>
       </c>
       <c r="N10" t="n">
-        <v>21.31954588842143</v>
+        <v>21.37983530935745</v>
       </c>
       <c r="O10" t="n">
-        <v>4.617309377594427</v>
+        <v>4.623833399827188</v>
       </c>
       <c r="P10" t="n">
-        <v>359.3454395753129</v>
+        <v>359.4078913299614</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37515,28 +37707,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2898630837557699</v>
+        <v>0.2846548830303572</v>
       </c>
       <c r="J11" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K11" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1689159889803423</v>
+        <v>0.1648514321740983</v>
       </c>
       <c r="M11" t="n">
-        <v>3.640890526940252</v>
+        <v>3.645430733632554</v>
       </c>
       <c r="N11" t="n">
-        <v>23.19645556364188</v>
+        <v>23.19502867499899</v>
       </c>
       <c r="O11" t="n">
-        <v>4.816269880690022</v>
+        <v>4.816121746280817</v>
       </c>
       <c r="P11" t="n">
-        <v>357.9238777849207</v>
+        <v>357.9763020390518</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37593,28 +37785,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3669772459320031</v>
+        <v>0.3611599099310462</v>
       </c>
       <c r="J12" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K12" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2164713377127229</v>
+        <v>0.2122226454216749</v>
       </c>
       <c r="M12" t="n">
-        <v>3.934003136052406</v>
+        <v>3.942887976157214</v>
       </c>
       <c r="N12" t="n">
-        <v>27.35233503389885</v>
+        <v>27.35882628390141</v>
       </c>
       <c r="O12" t="n">
-        <v>5.229945987665537</v>
+        <v>5.230566535653802</v>
       </c>
       <c r="P12" t="n">
-        <v>362.3566651203402</v>
+        <v>362.4152199903546</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37671,28 +37863,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3756773698562406</v>
+        <v>0.3698968146048602</v>
       </c>
       <c r="J13" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K13" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2369991021398751</v>
+        <v>0.2325756052750856</v>
       </c>
       <c r="M13" t="n">
-        <v>3.954280635089642</v>
+        <v>3.963984603323936</v>
       </c>
       <c r="N13" t="n">
-        <v>25.49588337495043</v>
+        <v>25.5105160727262</v>
       </c>
       <c r="O13" t="n">
-        <v>5.049344846111269</v>
+        <v>5.05079360820913</v>
       </c>
       <c r="P13" t="n">
-        <v>360.481350536949</v>
+        <v>360.5395369132493</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37749,28 +37941,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2438430955071395</v>
+        <v>0.2413212732150621</v>
       </c>
       <c r="J14" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K14" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09135550961770111</v>
+        <v>0.09058414210714938</v>
       </c>
       <c r="M14" t="n">
-        <v>4.468898053752834</v>
+        <v>4.457719325483835</v>
       </c>
       <c r="N14" t="n">
-        <v>33.18500022589767</v>
+        <v>33.03605530413025</v>
       </c>
       <c r="O14" t="n">
-        <v>5.760642344903706</v>
+        <v>5.747700001229209</v>
       </c>
       <c r="P14" t="n">
-        <v>363.9485009358631</v>
+        <v>363.9738841645818</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37827,28 +38019,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07210192911722804</v>
+        <v>0.07324388933013289</v>
       </c>
       <c r="J15" t="n">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K15" t="n">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005633347159461399</v>
+        <v>0.005883569968749836</v>
       </c>
       <c r="M15" t="n">
-        <v>5.581977384709472</v>
+        <v>5.557945524288692</v>
       </c>
       <c r="N15" t="n">
-        <v>51.21022117617521</v>
+        <v>50.93966166029886</v>
       </c>
       <c r="O15" t="n">
-        <v>7.156131718755267</v>
+        <v>7.137202649518848</v>
       </c>
       <c r="P15" t="n">
-        <v>397.9195905773151</v>
+        <v>397.9080481387472</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37886,7 +38078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P554"/>
+  <dimension ref="A1:P557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83309,6 +83501,252 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-34.82956581454231,173.41110734225583</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-34.830263229904006,173.41086499683738</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-34.83098134811873,173.41083653144477</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-34.83167451409864,173.4111329146019</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-34.832336145329016,173.41148254385504</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-34.83295232437949,173.41194157862432</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-34.83345048629513,173.41259073384367</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-34.833909814235945,173.41328918018598</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-34.83425819174867,173.41408302247316</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-34.83449361593681,173.41493299774726</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-34.834612449822274,173.4158214455189</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>-34.83473291785781,173.41670660293423</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>-34.83481201894547,173.41759086498092</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>-34.83434827565432,173.41836986242714</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-34.82956645767753,173.41110973352684</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-34.83026420418271,173.41087443748825</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-34.83098006057484,173.41084669207208</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-34.83167283945936,173.4111393837125</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-34.83233481808225,173.41148552759972</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-34.83294826408886,173.41194700463654</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-34.83344768473919,173.4125934892667</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-34.83390407608524,173.41329352156745</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-34.83425108827753,173.41408651471608</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-34.83448622406821,173.4149354567742</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-34.83460695772733,173.41582271444722</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-34.834727203750454,173.41670758517628</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-34.834801662902706,173.41759020908373</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>-34.83434363371386,173.41836848281713</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-34.82957227385472,173.41113135893582</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-34.830264741715474,173.4108796461233</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-34.830980786530546,173.4108409632078</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-34.83167537842846,173.41112957570598</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-34.83233850012149,173.41147725011427</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-34.83295262738625,173.41194117369798</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-34.83345356800657,173.41258770287817</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-34.83390797802773,173.4132905694281</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-34.834254598227986,173.41408478913732</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-34.83449005044725,173.4149341838662</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-34.83460642623428,173.4158228372467</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-34.83473381068706,173.41670644945887</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-34.83480463463672,173.4175903972977</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>-34.834348888740806,173.4183700446398</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P557"/>
+  <dimension ref="A1:P563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30528,6 +30528,330 @@
         <v>400.65</v>
       </c>
       <c r="P557" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="C558" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="D558" t="n">
+        <v>361.33</v>
+      </c>
+      <c r="E558" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="F558" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="G558" t="n">
+        <v>368.22</v>
+      </c>
+      <c r="H558" t="n">
+        <v>364.86</v>
+      </c>
+      <c r="I558" t="n">
+        <v>363.9</v>
+      </c>
+      <c r="J558" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="K558" t="n">
+        <v>359.86</v>
+      </c>
+      <c r="L558" t="n">
+        <v>365.95</v>
+      </c>
+      <c r="M558" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="N558" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="O558" t="n">
+        <v>399.64</v>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="C559" t="n">
+        <v>372</v>
+      </c>
+      <c r="D559" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="E559" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="F559" t="n">
+        <v>373.06</v>
+      </c>
+      <c r="G559" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="H559" t="n">
+        <v>364.76</v>
+      </c>
+      <c r="I559" t="n">
+        <v>363.8</v>
+      </c>
+      <c r="J559" t="n">
+        <v>361.61</v>
+      </c>
+      <c r="K559" t="n">
+        <v>359.76</v>
+      </c>
+      <c r="L559" t="n">
+        <v>366.04</v>
+      </c>
+      <c r="M559" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="N559" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="O559" t="n">
+        <v>398.89</v>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="C560" t="n">
+        <v>372</v>
+      </c>
+      <c r="D560" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="E560" t="n">
+        <v>369.44</v>
+      </c>
+      <c r="F560" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="G560" t="n">
+        <v>369.03</v>
+      </c>
+      <c r="H560" t="n">
+        <v>365.23</v>
+      </c>
+      <c r="I560" t="n">
+        <v>364.51</v>
+      </c>
+      <c r="J560" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="K560" t="n">
+        <v>360.38</v>
+      </c>
+      <c r="L560" t="n">
+        <v>366.85</v>
+      </c>
+      <c r="M560" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="N560" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="O560" t="n">
+        <v>401.03</v>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="C561" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="D561" t="n">
+        <v>362</v>
+      </c>
+      <c r="E561" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="F561" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="G561" t="n">
+        <v>369.22</v>
+      </c>
+      <c r="H561" t="n">
+        <v>365.39</v>
+      </c>
+      <c r="I561" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="J561" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="K561" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="L561" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="M561" t="n">
+        <v>363.95</v>
+      </c>
+      <c r="N561" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="O561" t="n">
+        <v>401.03</v>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="C562" t="n">
+        <v>372.22</v>
+      </c>
+      <c r="D562" t="n">
+        <v>362</v>
+      </c>
+      <c r="E562" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="F562" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="G562" t="n">
+        <v>369.22</v>
+      </c>
+      <c r="H562" t="n">
+        <v>365.39</v>
+      </c>
+      <c r="I562" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="J562" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="K562" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="L562" t="n">
+        <v>365.23</v>
+      </c>
+      <c r="M562" t="n">
+        <v>364.13</v>
+      </c>
+      <c r="N562" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="O562" t="n">
+        <v>401.55</v>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>373.06</v>
+      </c>
+      <c r="C563" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="D563" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="E563" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="F563" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="G563" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="H563" t="n">
+        <v>365.77</v>
+      </c>
+      <c r="I563" t="n">
+        <v>365.15</v>
+      </c>
+      <c r="J563" t="n">
+        <v>363.56</v>
+      </c>
+      <c r="K563" t="n">
+        <v>361</v>
+      </c>
+      <c r="L563" t="n">
+        <v>365.24</v>
+      </c>
+      <c r="M563" t="n">
+        <v>364.19</v>
+      </c>
+      <c r="N563" t="n">
+        <v>368.18</v>
+      </c>
+      <c r="O563" t="n">
+        <v>400.18</v>
+      </c>
+      <c r="P563" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30544,7 +30868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36837,6 +37161,66 @@
       </c>
       <c r="B629" t="n">
         <v>-0.49</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -37005,28 +37389,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2766300775670157</v>
+        <v>0.2820906629487501</v>
       </c>
       <c r="J2" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K2" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1060395404686491</v>
+        <v>0.1119928309961397</v>
       </c>
       <c r="M2" t="n">
-        <v>4.547210253391558</v>
+        <v>4.530119123837335</v>
       </c>
       <c r="N2" t="n">
-        <v>36.45321955290803</v>
+        <v>36.13904746527884</v>
       </c>
       <c r="O2" t="n">
-        <v>6.037650168145554</v>
+        <v>6.011576121557377</v>
       </c>
       <c r="P2" t="n">
-        <v>361.7366593872245</v>
+        <v>361.6814680336302</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37083,28 +37467,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1908786817693856</v>
+        <v>0.1847877670693383</v>
       </c>
       <c r="J3" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1065184790675167</v>
+        <v>0.1022387920355176</v>
       </c>
       <c r="M3" t="n">
-        <v>3.311442581716419</v>
+        <v>3.308673716277138</v>
       </c>
       <c r="N3" t="n">
-        <v>17.29848286140666</v>
+        <v>17.20273584521035</v>
       </c>
       <c r="O3" t="n">
-        <v>4.159144486719193</v>
+        <v>4.147618092979434</v>
       </c>
       <c r="P3" t="n">
-        <v>369.9367597534207</v>
+        <v>369.9982533687675</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37161,28 +37545,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1888046126246037</v>
+        <v>0.1707289378559055</v>
       </c>
       <c r="J4" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K4" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07542125385895315</v>
+        <v>0.06215178312837288</v>
       </c>
       <c r="M4" t="n">
-        <v>3.934049142740071</v>
+        <v>3.986849439351316</v>
       </c>
       <c r="N4" t="n">
-        <v>24.69232470047101</v>
+        <v>25.19221015895773</v>
       </c>
       <c r="O4" t="n">
-        <v>4.969137218921511</v>
+        <v>5.019184212494868</v>
       </c>
       <c r="P4" t="n">
-        <v>365.6023503398782</v>
+        <v>365.7849868686102</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37239,28 +37623,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2184073857304746</v>
+        <v>0.2046189438222751</v>
       </c>
       <c r="J5" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K5" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08925195657897678</v>
+        <v>0.0797946507110886</v>
       </c>
       <c r="M5" t="n">
-        <v>4.391634611089477</v>
+        <v>4.410856622293083</v>
       </c>
       <c r="N5" t="n">
-        <v>27.5043739236372</v>
+        <v>27.65512860870147</v>
       </c>
       <c r="O5" t="n">
-        <v>5.244461261525077</v>
+        <v>5.258814372907782</v>
       </c>
       <c r="P5" t="n">
-        <v>370.1239952106598</v>
+        <v>370.2633123013288</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37317,28 +37701,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2134535556108815</v>
+        <v>0.1984176744171913</v>
       </c>
       <c r="J6" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K6" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09731563782249941</v>
+        <v>0.08538391896665343</v>
       </c>
       <c r="M6" t="n">
-        <v>3.77500317841543</v>
+        <v>3.808621699881877</v>
       </c>
       <c r="N6" t="n">
-        <v>23.88068024892628</v>
+        <v>24.15441304894531</v>
       </c>
       <c r="O6" t="n">
-        <v>4.886786290490538</v>
+        <v>4.914713933582026</v>
       </c>
       <c r="P6" t="n">
-        <v>375.085809033248</v>
+        <v>375.2377292924443</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37395,28 +37779,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3213400906349935</v>
+        <v>0.3047471309679968</v>
       </c>
       <c r="J7" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K7" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.211373530255428</v>
+        <v>0.193428961986111</v>
       </c>
       <c r="M7" t="n">
-        <v>3.50876233637313</v>
+        <v>3.550057497887911</v>
       </c>
       <c r="N7" t="n">
-        <v>21.76893556283668</v>
+        <v>22.18060578650613</v>
       </c>
       <c r="O7" t="n">
-        <v>4.665719190311037</v>
+        <v>4.709629049777289</v>
       </c>
       <c r="P7" t="n">
-        <v>368.3464386755548</v>
+        <v>368.5140910688766</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37473,28 +37857,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2588261869855971</v>
+        <v>0.2516625991950009</v>
       </c>
       <c r="J8" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K8" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1523285341359235</v>
+        <v>0.1475331421899094</v>
       </c>
       <c r="M8" t="n">
-        <v>3.638777916854956</v>
+        <v>3.632102947529822</v>
       </c>
       <c r="N8" t="n">
-        <v>21.0644125223758</v>
+        <v>20.96033871037172</v>
       </c>
       <c r="O8" t="n">
-        <v>4.589598296406321</v>
+        <v>4.578246248332621</v>
       </c>
       <c r="P8" t="n">
-        <v>361.7895857260176</v>
+        <v>361.8619624164107</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37551,28 +37935,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3125921826086395</v>
+        <v>0.3024746432940968</v>
       </c>
       <c r="J9" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K9" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2148775414242455</v>
+        <v>0.2059834089103464</v>
       </c>
       <c r="M9" t="n">
-        <v>3.574041424009888</v>
+        <v>3.579880445226538</v>
       </c>
       <c r="N9" t="n">
-        <v>20.17387015521508</v>
+        <v>20.19985779580005</v>
       </c>
       <c r="O9" t="n">
-        <v>4.491533163098663</v>
+        <v>4.494425190811396</v>
       </c>
       <c r="P9" t="n">
-        <v>361.056527104756</v>
+        <v>361.1587481584811</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37629,28 +38013,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.324474812811705</v>
+        <v>0.3131114821107879</v>
       </c>
       <c r="J10" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K10" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2176839805019983</v>
+        <v>0.2074015477865088</v>
       </c>
       <c r="M10" t="n">
-        <v>3.446475027597873</v>
+        <v>3.466449016970617</v>
       </c>
       <c r="N10" t="n">
-        <v>21.37983530935745</v>
+        <v>21.45913659899935</v>
       </c>
       <c r="O10" t="n">
-        <v>4.623833399827188</v>
+        <v>4.63240073817015</v>
       </c>
       <c r="P10" t="n">
-        <v>359.4078913299614</v>
+        <v>359.5226942402255</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37707,28 +38091,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2846548830303572</v>
+        <v>0.2738622279265577</v>
       </c>
       <c r="J11" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K11" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1648514321740983</v>
+        <v>0.1561139318926256</v>
       </c>
       <c r="M11" t="n">
-        <v>3.645430733632554</v>
+        <v>3.656084822185783</v>
       </c>
       <c r="N11" t="n">
-        <v>23.19502867499899</v>
+        <v>23.22092193932516</v>
       </c>
       <c r="O11" t="n">
-        <v>4.816121746280817</v>
+        <v>4.818809182705325</v>
       </c>
       <c r="P11" t="n">
-        <v>357.9763020390518</v>
+        <v>358.0853462437567</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37785,28 +38169,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3611599099310462</v>
+        <v>0.3478756200586081</v>
       </c>
       <c r="J12" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K12" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2122226454216749</v>
+        <v>0.2014089441107934</v>
       </c>
       <c r="M12" t="n">
-        <v>3.942887976157214</v>
+        <v>3.968575467048144</v>
       </c>
       <c r="N12" t="n">
-        <v>27.35882628390141</v>
+        <v>27.48316249738293</v>
       </c>
       <c r="O12" t="n">
-        <v>5.230566535653802</v>
+        <v>5.242438602156723</v>
       </c>
       <c r="P12" t="n">
-        <v>362.4152199903546</v>
+        <v>362.5494609481977</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37863,28 +38247,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3698968146048602</v>
+        <v>0.3560603358427114</v>
       </c>
       <c r="J13" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K13" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2325756052750856</v>
+        <v>0.2203951558609122</v>
       </c>
       <c r="M13" t="n">
-        <v>3.963984603323936</v>
+        <v>3.995743349280027</v>
       </c>
       <c r="N13" t="n">
-        <v>25.5105160727262</v>
+        <v>25.68577702124363</v>
       </c>
       <c r="O13" t="n">
-        <v>5.05079360820913</v>
+        <v>5.068113753778976</v>
       </c>
       <c r="P13" t="n">
-        <v>360.5395369132493</v>
+        <v>360.6793391375535</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37941,28 +38325,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2413212732150621</v>
+        <v>0.2353891644581969</v>
       </c>
       <c r="J14" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K14" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09058414210714938</v>
+        <v>0.08830030272068312</v>
       </c>
       <c r="M14" t="n">
-        <v>4.457719325483835</v>
+        <v>4.440118405597273</v>
       </c>
       <c r="N14" t="n">
-        <v>33.03605530413025</v>
+        <v>32.76691710205146</v>
       </c>
       <c r="O14" t="n">
-        <v>5.747700001229209</v>
+        <v>5.724239434374794</v>
       </c>
       <c r="P14" t="n">
-        <v>363.9738841645818</v>
+        <v>364.033817993111</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38019,28 +38403,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07324388933013289</v>
+        <v>0.07439157792465172</v>
       </c>
       <c r="J15" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K15" t="n">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005883569968749836</v>
+        <v>0.006215427773596183</v>
       </c>
       <c r="M15" t="n">
-        <v>5.557945524288692</v>
+        <v>5.50881748382749</v>
       </c>
       <c r="N15" t="n">
-        <v>50.93966166029886</v>
+        <v>50.40685165271084</v>
       </c>
       <c r="O15" t="n">
-        <v>7.137202649518848</v>
+        <v>7.099778281940278</v>
       </c>
       <c r="P15" t="n">
-        <v>397.9080481387472</v>
+        <v>397.8963901267776</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38078,7 +38462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P557"/>
+  <dimension ref="A1:P563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83747,6 +84131,498 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-34.829575014167645,173.4111415478315</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-34.83026368904693,173.4108694458797</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-34.830983347919286,173.4108207500443</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-34.83168113162147,173.41110735117832</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-34.83234196808817,173.41146945387732</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-34.83295711188606,173.41193518078828</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-34.833457490184685,173.41258384528535</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-34.833909814235945,173.41328918018598</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-34.834261450988315,173.41408142014973</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-34.834497703205294,173.41493163804984</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-34.83461484154103,173.41582089292103</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-34.83474631029683,173.41670430080376</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>-34.834811028367454,173.41759080224293</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>-34.83435773470276,173.41837267370832</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-34.82957722319478,173.4111497613295</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-34.83026457373651,173.41087801842485</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-34.830982553478215,173.4108270193679</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-34.83168132069347,173.41110662079473</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-34.83234192527377,173.41146955012718</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-34.83295577865641,173.4119369624642</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-34.83345819057362,173.4125831564295</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-34.83391057932268,173.4132886013351</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-34.834260615285835,173.4140818310019</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-34.83449857283689,173.41493134875248</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-34.83461404430146,173.41582107712034</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-34.834748095955376,173.41670399385296</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>-34.834816161362575,173.41759112733985</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>-34.83436430348635,173.41837462598735</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-34.82957722319478,173.4111497613295</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-34.83026457373651,173.41087801842485</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-34.830982553478215,173.4108270193679</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-34.83167970007618,173.41111288122542</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-34.832339656110435,173.4114746513687</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-34.8329522031768,173.4119417405948</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-34.8334548987456,173.41258639405208</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-34.833905147206714,173.4132927111763</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-34.834252258261024,173.41408593952318</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-34.83449318112101,173.4149331423959</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-34.834606869145155,173.4158227349138</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-34.834743096111474,173.41670485331514</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>-34.83481174878783,173.41759084787054</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>-34.83434556055707,173.4183690554854</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-34.829578117990415,173.41115308831618</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-34.830264820105654,173.41088040571591</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-34.83098243020285,173.41082799219396</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-34.831679483993845,173.41111371594948</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-34.832338757007925,173.41147667261527</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-34.83295105175111,173.41194327931476</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-34.833453778123264,173.41258749622142</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-34.83390354052449,173.41329392676303</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-34.8342496675833,173.4140872131646</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-34.83449170274729,173.41493363420136</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-34.834626268641756,173.41581825273084</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>-34.83474104260414,173.41670520630848</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>-34.83481174878783,173.41759084787054</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>-34.83434556055707,173.4183690554854</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-34.829578117990415,173.41115308831618</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-34.830264820105654,173.41088040571591</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-34.83098243020285,173.41082799219396</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-34.831679483993845,173.41111371594948</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-34.832338757007925,173.41147667261527</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-34.83295105175111,173.41194327931476</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-34.833453778123264,173.41258749622142</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-34.83390116875549,173.41329572120048</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-34.834246157632805,173.4140889387432</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-34.834490224373575,173.41493412600676</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-34.83462121945772,173.4158194193266</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-34.834739435511466,173.41670548256414</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-34.83480841684364,173.41759063684273</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-34.83434100620038,173.4183677019059</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-34.829581864946164,173.41116702007358</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-34.83026558160998,173.41088778461574</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-34.830981224843285,173.41083750427083</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-34.83167853863358,173.41111736786723</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-34.83233695880281,173.41148071510827</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-34.83294844589292,173.4119467616808</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-34.83345111664519,173.41259011387348</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-34.833900250651354,173.41329641582143</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-34.83424431908729,173.4140898426176</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-34.8344877894051,173.41493493603912</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-34.83462113087555,173.4158194397932</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>-34.83473889981391,173.41670557464937</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>-34.83480490479435,173.41759041440804</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>-34.834353005178556,173.41837126806766</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P563"/>
+  <dimension ref="A1:P565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30852,6 +30852,114 @@
         <v>400.18</v>
       </c>
       <c r="P563" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:11:38+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="C564" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="D564" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="E564" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="F564" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="G564" t="n">
+        <v>369.31</v>
+      </c>
+      <c r="H564" t="n">
+        <v>365.46</v>
+      </c>
+      <c r="I564" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="J564" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="K564" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="L564" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="M564" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="N564" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="O564" t="n">
+        <v>399.64</v>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="C565" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="D565" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="E565" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="F565" t="n">
+        <v>377.69</v>
+      </c>
+      <c r="G565" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="H565" t="n">
+        <v>366.29</v>
+      </c>
+      <c r="I565" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="J565" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="K565" t="n">
+        <v>362.7</v>
+      </c>
+      <c r="L565" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="M565" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="N565" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="O565" t="n">
+        <v>401.76</v>
+      </c>
+      <c r="P565" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30868,7 +30976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B635"/>
+  <dimension ref="A1:B637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37221,6 +37329,26 @@
       </c>
       <c r="B635" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>
@@ -37389,28 +37517,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2820906629487501</v>
+        <v>0.2855886998092115</v>
       </c>
       <c r="J2" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K2" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1119928309961397</v>
+        <v>0.115030735537386</v>
       </c>
       <c r="M2" t="n">
-        <v>4.530119123837335</v>
+        <v>4.534072628522966</v>
       </c>
       <c r="N2" t="n">
-        <v>36.13904746527884</v>
+        <v>36.09876739158934</v>
       </c>
       <c r="O2" t="n">
-        <v>6.011576121557377</v>
+        <v>6.008224978443246</v>
       </c>
       <c r="P2" t="n">
-        <v>361.6814680336302</v>
+        <v>361.6459802683156</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37467,28 +37595,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1847877670693383</v>
+        <v>0.1844979025529876</v>
       </c>
       <c r="J3" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K3" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1022387920355176</v>
+        <v>0.1026799511071728</v>
       </c>
       <c r="M3" t="n">
-        <v>3.308673716277138</v>
+        <v>3.298511869292969</v>
       </c>
       <c r="N3" t="n">
-        <v>17.20273584521035</v>
+        <v>17.1423058752873</v>
       </c>
       <c r="O3" t="n">
-        <v>4.147618092979434</v>
+        <v>4.140326783635237</v>
       </c>
       <c r="P3" t="n">
-        <v>369.9982533687675</v>
+        <v>370.0011916368763</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37545,28 +37673,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1707289378559055</v>
+        <v>0.1663498543020424</v>
       </c>
       <c r="J4" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K4" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06215178312837288</v>
+        <v>0.05932589267431099</v>
       </c>
       <c r="M4" t="n">
-        <v>3.986849439351316</v>
+        <v>3.995708817913648</v>
       </c>
       <c r="N4" t="n">
-        <v>25.19221015895773</v>
+        <v>25.24269974333607</v>
       </c>
       <c r="O4" t="n">
-        <v>5.019184212494868</v>
+        <v>5.024211355360767</v>
       </c>
       <c r="P4" t="n">
-        <v>365.7849868686102</v>
+        <v>365.8294103508184</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37623,28 +37751,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2046189438222751</v>
+        <v>0.2006627479283013</v>
       </c>
       <c r="J5" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K5" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0797946507110886</v>
+        <v>0.07725025628333992</v>
       </c>
       <c r="M5" t="n">
-        <v>4.410856622293083</v>
+        <v>4.414108078849908</v>
       </c>
       <c r="N5" t="n">
-        <v>27.65512860870147</v>
+        <v>27.67028029957602</v>
       </c>
       <c r="O5" t="n">
-        <v>5.258814372907782</v>
+        <v>5.260254775158331</v>
       </c>
       <c r="P5" t="n">
-        <v>370.2633123013288</v>
+        <v>370.3034464554709</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37701,28 +37829,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1984176744171913</v>
+        <v>0.1961420626287214</v>
       </c>
       <c r="J6" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K6" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08538391896665343</v>
+        <v>0.0840917011026503</v>
       </c>
       <c r="M6" t="n">
-        <v>3.808621699881877</v>
+        <v>3.80645427995441</v>
       </c>
       <c r="N6" t="n">
-        <v>24.15441304894531</v>
+        <v>24.10662298606195</v>
       </c>
       <c r="O6" t="n">
-        <v>4.914713933582026</v>
+        <v>4.909849588944853</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2377292924443</v>
+        <v>375.2608140619446</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37779,28 +37907,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3047471309679968</v>
+        <v>0.2998575464755094</v>
       </c>
       <c r="J7" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K7" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L7" t="n">
-        <v>0.193428961986111</v>
+        <v>0.1884669165844139</v>
       </c>
       <c r="M7" t="n">
-        <v>3.550057497887911</v>
+        <v>3.561179009215893</v>
       </c>
       <c r="N7" t="n">
-        <v>22.18060578650613</v>
+        <v>22.27394350529721</v>
       </c>
       <c r="O7" t="n">
-        <v>4.709629049777289</v>
+        <v>4.719527890085746</v>
       </c>
       <c r="P7" t="n">
-        <v>368.5140910688766</v>
+        <v>368.5636949994417</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37857,28 +37985,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2516625991950009</v>
+        <v>0.2497972340635025</v>
       </c>
       <c r="J8" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K8" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1475331421899094</v>
+        <v>0.1465143186037406</v>
       </c>
       <c r="M8" t="n">
-        <v>3.632102947529822</v>
+        <v>3.62766900136267</v>
       </c>
       <c r="N8" t="n">
-        <v>20.96033871037172</v>
+        <v>20.91160967386461</v>
       </c>
       <c r="O8" t="n">
-        <v>4.578246248332621</v>
+        <v>4.572921350063284</v>
       </c>
       <c r="P8" t="n">
-        <v>361.8619624164107</v>
+        <v>361.8808852999439</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37935,28 +38063,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3024746432940968</v>
+        <v>0.3002033268397795</v>
       </c>
       <c r="J9" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K9" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2059834089103464</v>
+        <v>0.2045164063038316</v>
       </c>
       <c r="M9" t="n">
-        <v>3.579880445226538</v>
+        <v>3.577057032933123</v>
       </c>
       <c r="N9" t="n">
-        <v>20.19985779580005</v>
+        <v>20.16648089953141</v>
       </c>
       <c r="O9" t="n">
-        <v>4.494425190811396</v>
+        <v>4.490710511659754</v>
       </c>
       <c r="P9" t="n">
-        <v>361.1587481584811</v>
+        <v>361.1817889136603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38013,28 +38141,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3131114821107879</v>
+        <v>0.3103655100694195</v>
       </c>
       <c r="J10" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K10" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2074015477865088</v>
+        <v>0.2054014531174616</v>
       </c>
       <c r="M10" t="n">
-        <v>3.466449016970617</v>
+        <v>3.468022719885198</v>
       </c>
       <c r="N10" t="n">
-        <v>21.45913659899935</v>
+        <v>21.43814507093648</v>
       </c>
       <c r="O10" t="n">
-        <v>4.63240073817015</v>
+        <v>4.630134454952305</v>
       </c>
       <c r="P10" t="n">
-        <v>359.5226942402255</v>
+        <v>359.5505505670321</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38091,28 +38219,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2738622279265577</v>
+        <v>0.2714946846521098</v>
       </c>
       <c r="J11" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K11" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1561139318926256</v>
+        <v>0.1546434702931576</v>
       </c>
       <c r="M11" t="n">
-        <v>3.656084822185783</v>
+        <v>3.654013631531872</v>
       </c>
       <c r="N11" t="n">
-        <v>23.22092193932516</v>
+        <v>23.18072586084975</v>
       </c>
       <c r="O11" t="n">
-        <v>4.818809182705325</v>
+        <v>4.814636628121561</v>
       </c>
       <c r="P11" t="n">
-        <v>358.0853462437567</v>
+        <v>358.1093627779229</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38169,28 +38297,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3478756200586081</v>
+        <v>0.3442624463539344</v>
       </c>
       <c r="J12" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K12" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2014089441107934</v>
+        <v>0.1987815467770639</v>
       </c>
       <c r="M12" t="n">
-        <v>3.968575467048144</v>
+        <v>3.972739967245118</v>
       </c>
       <c r="N12" t="n">
-        <v>27.48316249738293</v>
+        <v>27.48211940771908</v>
       </c>
       <c r="O12" t="n">
-        <v>5.242438602156723</v>
+        <v>5.242339116054882</v>
       </c>
       <c r="P12" t="n">
-        <v>362.5494609481977</v>
+        <v>362.5861139944228</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38247,28 +38375,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3560603358427114</v>
+        <v>0.3517109291947892</v>
       </c>
       <c r="J13" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K13" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2203951558609122</v>
+        <v>0.2166445112897292</v>
       </c>
       <c r="M13" t="n">
-        <v>3.995743349280027</v>
+        <v>4.004713334425618</v>
       </c>
       <c r="N13" t="n">
-        <v>25.68577702124363</v>
+        <v>25.73232166615919</v>
       </c>
       <c r="O13" t="n">
-        <v>5.068113753778976</v>
+        <v>5.07270358548173</v>
       </c>
       <c r="P13" t="n">
-        <v>360.6793391375535</v>
+        <v>360.7234617378134</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38325,28 +38453,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2353891644581969</v>
+        <v>0.2350672147437592</v>
       </c>
       <c r="J14" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K14" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08830030272068312</v>
+        <v>0.08871409867912927</v>
       </c>
       <c r="M14" t="n">
-        <v>4.440118405597273</v>
+        <v>4.427623806428461</v>
       </c>
       <c r="N14" t="n">
-        <v>32.76691710205146</v>
+        <v>32.65443496462724</v>
       </c>
       <c r="O14" t="n">
-        <v>5.724239434374794</v>
+        <v>5.714405915283516</v>
       </c>
       <c r="P14" t="n">
-        <v>364.033817993111</v>
+        <v>364.0370814306114</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38403,28 +38531,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07439157792465172</v>
+        <v>0.07497358298108588</v>
       </c>
       <c r="J15" t="n">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K15" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006215427773596183</v>
+        <v>0.006362012774695391</v>
       </c>
       <c r="M15" t="n">
-        <v>5.50881748382749</v>
+        <v>5.493223818415971</v>
       </c>
       <c r="N15" t="n">
-        <v>50.40685165271084</v>
+        <v>50.23421820776349</v>
       </c>
       <c r="O15" t="n">
-        <v>7.099778281940278</v>
+        <v>7.08761019016731</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8963901267776</v>
+        <v>397.8904578558395</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38462,7 +38590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P563"/>
+  <dimension ref="A1:P565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84623,6 +84751,170 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-09 22:11:38+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-34.82958480099247,173.41117793675005</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-34.83026719420588,173.41090341052163</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-34.83098067695234,173.41084182794205</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-34.83167940296297,173.411114028971</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-34.83232586986827,173.4115056438112</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-34.83295050633894,173.4119440081821</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-34.83345328785099,173.4125879784205</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-34.8338986439691,173.41329763140803</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-34.834245739781565,173.41408914416922</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-34.83448570228924,173.41493563035255</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-34.834616613184565,173.41582048358927</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>-34.83474773882367,173.41670405524314</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>-34.8347983309585,173.41758999805594</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>-34.83435773470276,173.41837267370832</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-34.82958519246524,173.41117939230696</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-34.830267530163106,173.41090666591876</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-34.830978567570746,173.41085847407567</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-34.83167678296423,173.41112414999998</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-34.83232210219824,173.4115141137937</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-34.832946870257686,173.41194886729735</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-34.83344747462249,173.4125936959234</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-34.833889768962145,173.41330434607596</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-34.83423704847547,173.4140934170298</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-34.834473005667746,173.41493985409187</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-34.834601288468,173.4158240243085</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>-34.83473506064805,173.4167062345934</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>-34.83478185134256,173.41758895432434</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>-34.83433916694093,173.41836715526807</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P565"/>
+  <dimension ref="A1:P567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30962,6 +30962,114 @@
       <c r="P565" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:26+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="C566" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="D566" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="E566" t="n">
+        <v>389.11</v>
+      </c>
+      <c r="F566" t="n">
+        <v>377.69</v>
+      </c>
+      <c r="G566" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="H566" t="n">
+        <v>366.29</v>
+      </c>
+      <c r="I566" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="J566" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="K566" t="n">
+        <v>362.7</v>
+      </c>
+      <c r="L566" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="M566" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="N566" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="O566" t="n">
+        <v>401.13</v>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="C567" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="D567" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="E567" t="n">
+        <v>403.25</v>
+      </c>
+      <c r="F567" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="G567" t="n">
+        <v>374.02</v>
+      </c>
+      <c r="H567" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="I567" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="J567" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="K567" t="n">
+        <v>362.7</v>
+      </c>
+      <c r="L567" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="M567" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="N567" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="O567" t="n">
+        <v>401.13</v>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30976,7 +31084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B637"/>
+  <dimension ref="A1:B639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37349,6 +37457,26 @@
       </c>
       <c r="B637" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -37517,28 +37645,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2855886998092115</v>
+        <v>0.2890568018947174</v>
       </c>
       <c r="J2" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K2" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L2" t="n">
-        <v>0.115030735537386</v>
+        <v>0.1180805142849167</v>
       </c>
       <c r="M2" t="n">
-        <v>4.534072628522966</v>
+        <v>4.538131352721238</v>
       </c>
       <c r="N2" t="n">
-        <v>36.09876739158934</v>
+        <v>36.05873938098772</v>
       </c>
       <c r="O2" t="n">
-        <v>6.008224978443246</v>
+        <v>6.00489295333295</v>
       </c>
       <c r="P2" t="n">
-        <v>361.6459802683156</v>
+        <v>361.6107434459232</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37595,28 +37723,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1844979025529876</v>
+        <v>0.1843118806815715</v>
       </c>
       <c r="J3" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K3" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1026799511071728</v>
+        <v>0.1032223166614328</v>
       </c>
       <c r="M3" t="n">
-        <v>3.298511869292969</v>
+        <v>3.28785220255452</v>
       </c>
       <c r="N3" t="n">
-        <v>17.1423058752873</v>
+        <v>17.08187754990243</v>
       </c>
       <c r="O3" t="n">
-        <v>4.140326783635237</v>
+        <v>4.133022810232534</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0011916368763</v>
+        <v>370.0030804415347</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37673,28 +37801,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1663498543020424</v>
+        <v>0.162587587439145</v>
       </c>
       <c r="J4" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K4" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05932589267431099</v>
+        <v>0.05702868675762029</v>
       </c>
       <c r="M4" t="n">
-        <v>3.995708817913648</v>
+        <v>4.001778884635751</v>
       </c>
       <c r="N4" t="n">
-        <v>25.24269974333607</v>
+        <v>25.2565097530134</v>
       </c>
       <c r="O4" t="n">
-        <v>5.024211355360767</v>
+        <v>5.025585513451482</v>
       </c>
       <c r="P4" t="n">
-        <v>365.8294103508184</v>
+        <v>365.867636035373</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37751,28 +37879,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2006627479283013</v>
+        <v>0.214902883596815</v>
       </c>
       <c r="J5" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K5" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07725025628333992</v>
+        <v>0.08367674849388196</v>
       </c>
       <c r="M5" t="n">
-        <v>4.414108078849908</v>
+        <v>4.474896567427181</v>
       </c>
       <c r="N5" t="n">
-        <v>27.67028029957602</v>
+        <v>29.2228014484495</v>
       </c>
       <c r="O5" t="n">
-        <v>5.260254775158331</v>
+        <v>5.40581182140569</v>
       </c>
       <c r="P5" t="n">
-        <v>370.3034464554709</v>
+        <v>370.1587144944111</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37829,28 +37957,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1961420626287214</v>
+        <v>0.1992962423703079</v>
       </c>
       <c r="J6" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K6" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0840917011026503</v>
+        <v>0.08635161138758618</v>
       </c>
       <c r="M6" t="n">
-        <v>3.80645427995441</v>
+        <v>3.819185908292009</v>
       </c>
       <c r="N6" t="n">
-        <v>24.10662298606195</v>
+        <v>24.28288693534539</v>
       </c>
       <c r="O6" t="n">
-        <v>4.909849588944853</v>
+        <v>4.927766931922145</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2608140619446</v>
+        <v>375.2287167079078</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37907,28 +38035,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2998575464755094</v>
+        <v>0.296693500590183</v>
       </c>
       <c r="J7" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K7" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1884669165844139</v>
+        <v>0.1858416767799579</v>
       </c>
       <c r="M7" t="n">
-        <v>3.561179009215893</v>
+        <v>3.563939891768032</v>
       </c>
       <c r="N7" t="n">
-        <v>22.27394350529721</v>
+        <v>22.28308248041924</v>
       </c>
       <c r="O7" t="n">
-        <v>4.719527890085746</v>
+        <v>4.720495999407185</v>
       </c>
       <c r="P7" t="n">
-        <v>368.5636949994417</v>
+        <v>368.5958285598641</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37985,28 +38113,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2497972340635025</v>
+        <v>0.24549874089705</v>
       </c>
       <c r="J8" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K8" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1465143186037406</v>
+        <v>0.1420848690808355</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62766900136267</v>
+        <v>3.634406431608269</v>
       </c>
       <c r="N8" t="n">
-        <v>20.91160967386461</v>
+        <v>21.02754082354074</v>
       </c>
       <c r="O8" t="n">
-        <v>4.572921350063284</v>
+        <v>4.585579660581718</v>
       </c>
       <c r="P8" t="n">
-        <v>361.8808852999439</v>
+        <v>361.9245862863405</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38063,28 +38191,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3002033268397795</v>
+        <v>0.2963194211931842</v>
       </c>
       <c r="J9" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K9" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2045164063038316</v>
+        <v>0.200461518561143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.577057032933123</v>
+        <v>3.581326309881328</v>
       </c>
       <c r="N9" t="n">
-        <v>20.16648089953141</v>
+        <v>20.23587737560816</v>
       </c>
       <c r="O9" t="n">
-        <v>4.490710511659754</v>
+        <v>4.49843054582464</v>
       </c>
       <c r="P9" t="n">
-        <v>361.1817889136603</v>
+        <v>361.2212707249947</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38141,28 +38269,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3103655100694195</v>
+        <v>0.3080269269554876</v>
       </c>
       <c r="J10" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K10" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2054014531174616</v>
+        <v>0.2039235416162862</v>
       </c>
       <c r="M10" t="n">
-        <v>3.468022719885198</v>
+        <v>3.467514437915958</v>
       </c>
       <c r="N10" t="n">
-        <v>21.43814507093648</v>
+        <v>21.40219087067203</v>
       </c>
       <c r="O10" t="n">
-        <v>4.630134454952305</v>
+        <v>4.626250195425235</v>
       </c>
       <c r="P10" t="n">
-        <v>359.5505505670321</v>
+        <v>359.5743112571107</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38219,28 +38347,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2714946846521098</v>
+        <v>0.2696740887101002</v>
       </c>
       <c r="J11" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K11" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1546434702931576</v>
+        <v>0.1537836978653917</v>
       </c>
       <c r="M11" t="n">
-        <v>3.654013631531872</v>
+        <v>3.649519189075887</v>
       </c>
       <c r="N11" t="n">
-        <v>23.18072586084975</v>
+        <v>23.12293605827471</v>
       </c>
       <c r="O11" t="n">
-        <v>4.814636628121561</v>
+        <v>4.80863141218733</v>
       </c>
       <c r="P11" t="n">
-        <v>358.1093627779229</v>
+        <v>358.1278605709377</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38297,28 +38425,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3442624463539344</v>
+        <v>0.3413131826967427</v>
       </c>
       <c r="J12" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K12" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1987815467770639</v>
+        <v>0.1969392932814736</v>
       </c>
       <c r="M12" t="n">
-        <v>3.972739967245118</v>
+        <v>3.973692344010991</v>
       </c>
       <c r="N12" t="n">
-        <v>27.48211940771908</v>
+        <v>27.44830793337</v>
       </c>
       <c r="O12" t="n">
-        <v>5.242339116054882</v>
+        <v>5.239113277394373</v>
       </c>
       <c r="P12" t="n">
-        <v>362.5861139944228</v>
+        <v>362.6160793708095</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38375,28 +38503,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3517109291947892</v>
+        <v>0.3479306634659942</v>
       </c>
       <c r="J13" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K13" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2166445112897292</v>
+        <v>0.213647056433526</v>
       </c>
       <c r="M13" t="n">
-        <v>4.004713334425618</v>
+        <v>4.010659951692179</v>
       </c>
       <c r="N13" t="n">
-        <v>25.73232166615919</v>
+        <v>25.74538936187986</v>
       </c>
       <c r="O13" t="n">
-        <v>5.07270358548173</v>
+        <v>5.073991462535177</v>
       </c>
       <c r="P13" t="n">
-        <v>360.7234617378134</v>
+        <v>360.7618703234992</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38453,28 +38581,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2350672147437592</v>
+        <v>0.2353807067305903</v>
       </c>
       <c r="J14" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K14" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08871409867912927</v>
+        <v>0.08957089529796114</v>
       </c>
       <c r="M14" t="n">
-        <v>4.427623806428461</v>
+        <v>4.413552211007486</v>
       </c>
       <c r="N14" t="n">
-        <v>32.65443496462724</v>
+        <v>32.53976358273028</v>
       </c>
       <c r="O14" t="n">
-        <v>5.714405915283516</v>
+        <v>5.70436355632513</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0370814306114</v>
+        <v>364.0338963015099</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38531,28 +38659,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07497358298108588</v>
+        <v>0.07583820787873743</v>
       </c>
       <c r="J15" t="n">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K15" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006362012774695391</v>
+        <v>0.006559398346293155</v>
       </c>
       <c r="M15" t="n">
-        <v>5.493223818415971</v>
+        <v>5.478413763697479</v>
       </c>
       <c r="N15" t="n">
-        <v>50.23421820776349</v>
+        <v>50.06179603418057</v>
       </c>
       <c r="O15" t="n">
-        <v>7.08761019016731</v>
+        <v>7.075436102049157</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8904578558395</v>
+        <v>397.8816364635649</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38590,7 +38718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P565"/>
+  <dimension ref="A1:P567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84915,6 +85043,170 @@
         </is>
       </c>
     </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:26+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-34.82958519246524,173.41117939230696</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-34.830267530163106,173.41090666591876</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-34.830978567570746,173.41085847407567</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-34.8316265706612,173.4113181188734</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-34.83232210219824,173.4115141137937</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-34.832946870257686,173.41194886729735</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-34.83344747462249,173.4125936959234</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-34.833889768962145,173.41330434607596</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-34.83423704847547,173.4140934170298</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-34.834473005667746,173.41493985409187</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-34.834601288468,173.4158240243085</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>-34.83473506064805,173.4167062345934</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>-34.83478185134256,173.41758895432434</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>-34.83434468471925,173.41836879518166</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-34.82958519246524,173.41117939230696</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-34.830267530163106,173.41090666591876</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-34.830978567570746,173.41085847407567</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-34.831588377772626,173.41146565609247</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-34.832259378968914,173.41165511963806</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-34.8329219630959,173.41198215222545</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-34.833503015457325,173.41253906962797</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-34.83393506209716,173.4132700781004</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-34.83423704847547,173.4140934170298</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-34.834473005667746,173.41493985409187</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-34.834601288468,173.4158240243085</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>-34.83473506064805,173.4167062345934</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>-34.83478185134256,173.41758895432434</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>-34.83434468471925,173.41836879518166</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P567"/>
+  <dimension ref="A1:P570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30981,7 +30981,7 @@
         <v>364.82</v>
       </c>
       <c r="E566" t="n">
-        <v>389.11</v>
+        <v>370.52</v>
       </c>
       <c r="F566" t="n">
         <v>377.69</v>
@@ -31022,54 +31022,216 @@
     <row r="567">
       <c r="A567" s="1" t="inlineStr">
         <is>
-          <t>2026-03-05 22:11:20+00:00</t>
+          <t>2026-03-21 22:11:10+00:00</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>374.25</v>
+        <v>372.97</v>
       </c>
       <c r="C567" t="n">
-        <v>374.64</v>
+        <v>373.92</v>
       </c>
       <c r="D567" t="n">
-        <v>364.82</v>
+        <v>364.37</v>
       </c>
       <c r="E567" t="n">
-        <v>403.25</v>
+        <v>370.56</v>
       </c>
       <c r="F567" t="n">
-        <v>392.34</v>
+        <v>377.56</v>
       </c>
       <c r="G567" t="n">
-        <v>374.02</v>
+        <v>369.5</v>
       </c>
       <c r="H567" t="n">
-        <v>358.36</v>
+        <v>365.2</v>
       </c>
       <c r="I567" t="n">
-        <v>360.6</v>
+        <v>367.15</v>
       </c>
       <c r="J567" t="n">
-        <v>364.43</v>
+        <v>365.56</v>
       </c>
       <c r="K567" t="n">
-        <v>362.7</v>
+        <v>363.92</v>
       </c>
       <c r="L567" t="n">
-        <v>367.48</v>
+        <v>368.52</v>
       </c>
       <c r="M567" t="n">
-        <v>364.62</v>
+        <v>365.64</v>
       </c>
       <c r="N567" t="n">
-        <v>370.74</v>
+        <v>371.52</v>
       </c>
       <c r="O567" t="n">
-        <v>401.13</v>
+        <v>401.39</v>
       </c>
       <c r="P567" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="C568" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="D568" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="E568" t="n">
+        <v>370.16</v>
+      </c>
+      <c r="F568" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="G568" t="n">
+        <v>371.65</v>
+      </c>
+      <c r="H568" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="I568" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="J568" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="K568" t="n">
+        <v>364.93</v>
+      </c>
+      <c r="L568" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="M568" t="n">
+        <v>366.72</v>
+      </c>
+      <c r="N568" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="O568" t="n">
+        <v>402.24</v>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>375.33</v>
+      </c>
+      <c r="C569" t="n">
+        <v>373.91</v>
+      </c>
+      <c r="D569" t="n">
+        <v>364</v>
+      </c>
+      <c r="E569" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="F569" t="n">
+        <v>378.97</v>
+      </c>
+      <c r="G569" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="H569" t="n">
+        <v>368.2</v>
+      </c>
+      <c r="I569" t="n">
+        <v>368.42</v>
+      </c>
+      <c r="J569" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="K569" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="L569" t="n">
+        <v>368.1</v>
+      </c>
+      <c r="M569" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="N569" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="O569" t="n">
+        <v>402.46</v>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="C570" t="n">
+        <v>373.82</v>
+      </c>
+      <c r="D570" t="n">
+        <v>364.67</v>
+      </c>
+      <c r="E570" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="F570" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="G570" t="n">
+        <v>372.27</v>
+      </c>
+      <c r="H570" t="n">
+        <v>368.19</v>
+      </c>
+      <c r="I570" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="J570" t="n">
+        <v>367.54</v>
+      </c>
+      <c r="K570" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="L570" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="M570" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="N570" t="n">
+        <v>370.85</v>
+      </c>
+      <c r="O570" t="n">
+        <v>400.68</v>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31084,7 +31246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B639"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37477,6 +37639,56 @@
       </c>
       <c r="B639" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -37645,28 +37857,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2890568018947174</v>
+        <v>0.2941550142986996</v>
       </c>
       <c r="J2" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K2" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1180805142849167</v>
+        <v>0.1226638497364279</v>
       </c>
       <c r="M2" t="n">
-        <v>4.538131352721238</v>
+        <v>4.543597563155107</v>
       </c>
       <c r="N2" t="n">
-        <v>36.05873938098772</v>
+        <v>35.99912086700491</v>
       </c>
       <c r="O2" t="n">
-        <v>6.00489295333295</v>
+        <v>5.999926738469805</v>
       </c>
       <c r="P2" t="n">
-        <v>361.6107434459232</v>
+        <v>361.5585878758817</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37723,28 +37935,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1843118806815715</v>
+        <v>0.1830567736580588</v>
       </c>
       <c r="J3" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K3" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1032223166614328</v>
+        <v>0.103027810969066</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28785220255452</v>
+        <v>3.27723361381081</v>
       </c>
       <c r="N3" t="n">
-        <v>17.08187754990243</v>
+        <v>16.99823773602411</v>
       </c>
       <c r="O3" t="n">
-        <v>4.133022810232534</v>
+        <v>4.122891914181611</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0030804415347</v>
+        <v>370.0158949101711</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37801,28 +38013,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.162587587439145</v>
+        <v>0.1562358299745437</v>
       </c>
       <c r="J4" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K4" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05702868675762029</v>
+        <v>0.0531028979022562</v>
       </c>
       <c r="M4" t="n">
-        <v>4.001778884635751</v>
+        <v>4.014684841955741</v>
       </c>
       <c r="N4" t="n">
-        <v>25.2565097530134</v>
+        <v>25.31837292200539</v>
       </c>
       <c r="O4" t="n">
-        <v>5.025585513451482</v>
+        <v>5.031736571205352</v>
       </c>
       <c r="P4" t="n">
-        <v>365.867636035373</v>
+        <v>365.932587531743</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37879,28 +38091,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.214902883596815</v>
+        <v>0.1911967092319349</v>
       </c>
       <c r="J5" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K5" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08367674849388196</v>
+        <v>0.07132105925913068</v>
       </c>
       <c r="M5" t="n">
-        <v>4.474896567427181</v>
+        <v>4.420293143376207</v>
       </c>
       <c r="N5" t="n">
-        <v>29.2228014484495</v>
+        <v>27.68844639725623</v>
       </c>
       <c r="O5" t="n">
-        <v>5.40581182140569</v>
+        <v>5.261981223575035</v>
       </c>
       <c r="P5" t="n">
-        <v>370.1587144944111</v>
+        <v>370.4000177529395</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37957,28 +38169,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1992962423703079</v>
+        <v>0.1923289521050873</v>
       </c>
       <c r="J6" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K6" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08635161138758618</v>
+        <v>0.08246476553434701</v>
       </c>
       <c r="M6" t="n">
-        <v>3.819185908292009</v>
+        <v>3.791711234797437</v>
       </c>
       <c r="N6" t="n">
-        <v>24.28288693534539</v>
+        <v>23.94052125339507</v>
       </c>
       <c r="O6" t="n">
-        <v>4.927766931922145</v>
+        <v>4.89290519562714</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2287167079078</v>
+        <v>375.2996863708145</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38035,28 +38247,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.296693500590183</v>
+        <v>0.2904919174285035</v>
       </c>
       <c r="J7" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K7" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1858416767799579</v>
+        <v>0.1801107154899415</v>
       </c>
       <c r="M7" t="n">
-        <v>3.563939891768032</v>
+        <v>3.575431514450494</v>
       </c>
       <c r="N7" t="n">
-        <v>22.28308248041924</v>
+        <v>22.34465813410229</v>
       </c>
       <c r="O7" t="n">
-        <v>4.720495999407185</v>
+        <v>4.727013659182961</v>
       </c>
       <c r="P7" t="n">
-        <v>368.5958285598641</v>
+        <v>368.6591813365393</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38113,28 +38325,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.24549874089705</v>
+        <v>0.247069043083307</v>
       </c>
       <c r="J8" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K8" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1420848690808355</v>
+        <v>0.1460531730952001</v>
       </c>
       <c r="M8" t="n">
-        <v>3.634406431608269</v>
+        <v>3.607990356820027</v>
       </c>
       <c r="N8" t="n">
-        <v>21.02754082354074</v>
+        <v>20.76091296784046</v>
       </c>
       <c r="O8" t="n">
-        <v>4.585579660581718</v>
+        <v>4.556414485957183</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9245862863405</v>
+        <v>361.9086775508464</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38191,28 +38403,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2963194211931842</v>
+        <v>0.2978648215922265</v>
       </c>
       <c r="J9" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K9" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.200461518561143</v>
+        <v>0.2050269284248342</v>
       </c>
       <c r="M9" t="n">
-        <v>3.581326309881328</v>
+        <v>3.555711589160965</v>
       </c>
       <c r="N9" t="n">
-        <v>20.23587737560816</v>
+        <v>20.01105068609781</v>
       </c>
       <c r="O9" t="n">
-        <v>4.49843054582464</v>
+        <v>4.473371288647725</v>
       </c>
       <c r="P9" t="n">
-        <v>361.2212707249947</v>
+        <v>361.2056037986019</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38269,28 +38481,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3080269269554876</v>
+        <v>0.3082163312041524</v>
       </c>
       <c r="J10" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K10" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2039235416162862</v>
+        <v>0.2061552182341947</v>
       </c>
       <c r="M10" t="n">
-        <v>3.467514437915958</v>
+        <v>3.448261044185096</v>
       </c>
       <c r="N10" t="n">
-        <v>21.40219087067203</v>
+        <v>21.27857323564442</v>
       </c>
       <c r="O10" t="n">
-        <v>4.626250195425235</v>
+        <v>4.612870390076489</v>
       </c>
       <c r="P10" t="n">
-        <v>359.5743112571107</v>
+        <v>359.5724104800668</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38347,28 +38559,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2696740887101002</v>
+        <v>0.2690744342699698</v>
       </c>
       <c r="J11" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K11" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1537836978653917</v>
+        <v>0.1547774778812711</v>
       </c>
       <c r="M11" t="n">
-        <v>3.649519189075887</v>
+        <v>3.632985489197389</v>
       </c>
       <c r="N11" t="n">
-        <v>23.12293605827471</v>
+        <v>22.9984261076068</v>
       </c>
       <c r="O11" t="n">
-        <v>4.80863141218733</v>
+        <v>4.795667430880378</v>
       </c>
       <c r="P11" t="n">
-        <v>358.1278605709377</v>
+        <v>358.1340214051842</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38425,28 +38637,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3413131826967427</v>
+        <v>0.3382949175613453</v>
       </c>
       <c r="J12" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K12" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1969392932814736</v>
+        <v>0.1957789803522999</v>
       </c>
       <c r="M12" t="n">
-        <v>3.973692344010991</v>
+        <v>3.967835465345224</v>
       </c>
       <c r="N12" t="n">
-        <v>27.44830793337</v>
+        <v>27.34577606062883</v>
       </c>
       <c r="O12" t="n">
-        <v>5.239113277394373</v>
+        <v>5.229318890699708</v>
       </c>
       <c r="P12" t="n">
-        <v>362.6160793708095</v>
+        <v>362.646968916808</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38503,28 +38715,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3479306634659942</v>
+        <v>0.344613064040842</v>
       </c>
       <c r="J13" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K13" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L13" t="n">
-        <v>0.213647056433526</v>
+        <v>0.2121225178092476</v>
       </c>
       <c r="M13" t="n">
-        <v>4.010659951692179</v>
+        <v>4.007078336549531</v>
       </c>
       <c r="N13" t="n">
-        <v>25.74538936187986</v>
+        <v>25.65814992883586</v>
       </c>
       <c r="O13" t="n">
-        <v>5.073991462535177</v>
+        <v>5.065387441137733</v>
       </c>
       <c r="P13" t="n">
-        <v>360.7618703234992</v>
+        <v>360.7958261932233</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38581,28 +38793,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2353807067305903</v>
+        <v>0.2366685738595347</v>
       </c>
       <c r="J14" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K14" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08957089529796114</v>
+        <v>0.09143188723710272</v>
       </c>
       <c r="M14" t="n">
-        <v>4.413552211007486</v>
+        <v>4.3966454175869</v>
       </c>
       <c r="N14" t="n">
-        <v>32.53976358273028</v>
+        <v>32.37657789340171</v>
       </c>
       <c r="O14" t="n">
-        <v>5.70436355632513</v>
+        <v>5.690041993992813</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0338963015099</v>
+        <v>364.0207400214246</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38659,28 +38871,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07583820787873743</v>
+        <v>0.07788427696453074</v>
       </c>
       <c r="J15" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K15" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006559398346293155</v>
+        <v>0.00699522643174233</v>
       </c>
       <c r="M15" t="n">
-        <v>5.478413763697479</v>
+        <v>5.460453688172776</v>
       </c>
       <c r="N15" t="n">
-        <v>50.06179603418057</v>
+        <v>49.82032961872514</v>
       </c>
       <c r="O15" t="n">
-        <v>7.075436102049157</v>
+        <v>7.058351763600702</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8816364635649</v>
+        <v>397.860635027625</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38718,7 +38930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P567"/>
+  <dimension ref="A1:P570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85066,7 +85278,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>-34.8316265706612,173.4113181188734</t>
+          <t>-34.83167678296423,173.41112414999998</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -85128,82 +85340,328 @@
     <row r="567">
       <c r="A567" s="1" t="inlineStr">
         <is>
-          <t>2026-03-05 22:11:20+00:00</t>
+          <t>2026-03-21 22:11:10+00:00</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>-34.82958519246524,173.41117939230696</t>
+          <t>-34.829581613285015,173.41116608435848</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>-34.830267530163106,173.41090666591876</t>
+          <t>-34.83026672386563,173.4108988529657</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>-34.830978567570746,173.41085847407567</t>
+          <t>-34.83097918394873,173.4108536099458</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>-34.831588377772626,173.41146565609247</t>
+          <t>-34.83167667492301,173.41112456736198</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>-34.832259378968914,173.41165511963806</t>
+          <t>-34.83232265878589,173.41151286254632</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>-34.8329219630959,173.41198215222545</t>
+          <t>-34.832949354913225,173.411945546902</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>-34.833503015457325,173.41253906962797</t>
+          <t>-34.833455108862275,173.41258618739533</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>-34.83393506209716,173.4132700781004</t>
+          <t>-34.83388494891511,173.41330799283466</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>-34.83423704847547,173.4140934170298</t>
+          <t>-34.83422760503694,173.41409805965614</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>-34.834473005667746,173.41493985409187</t>
+          <t>-34.834462396162,173.4149433835169</t>
         </is>
       </c>
       <c r="L567" t="inlineStr">
         <is>
-          <t>-34.834601288468,173.4158240243085</t>
+          <t>-34.83459207592159,173.41582615283275</t>
         </is>
       </c>
       <c r="M567" t="inlineStr">
         <is>
-          <t>-34.83473506064805,173.4167062345934</t>
+          <t>-34.83472595378947,173.41670780004173</t>
         </is>
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>-34.83478185134256,173.41758895432434</t>
+          <t>-34.834774827243955,173.41758850945527</t>
         </is>
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>-34.83434468471925,173.41836879518166</t>
+          <t>-34.8343424075409,173.4183681183919</t>
         </is>
       </c>
       <c r="P567" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:17:10+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-34.82958572374967,173.41118136770564</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-34.83026697023435,173.4109012402569</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-34.83097967705097,173.41084971864186</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-34.83167775533498,173.4111203937419</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-34.83232051806407,173.4115176750361</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-34.832936325620956,173.41196295872922</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-34.833443342327364,173.41259776017196</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-34.83387523231202,173.41331534423585</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-34.83421005528345,173.41410668754304</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>-34.834453612882555,173.41494630541726</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>-34.834589329874085,173.4158267872966</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>-34.834716311233294,173.41670945757494</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>-34.834771045036995,173.4175882699104</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>-34.834334962919336,173.41836590581028</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-34.829588212397404,173.41119062088933</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-34.83026671266704,173.41089874445245</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-34.83097969074825,173.41084961055006</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-34.831679889148205,173.41111215084186</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-34.832316621949865,173.41152643376682</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-34.83293311374853,173.41196725094625</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-34.833434097192026,173.41260685306557</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-34.83387523231202,173.41331534423585</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-34.83421005528345,173.41410668754304</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>-34.83446178741986,173.41494358602486</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>-34.83459579637303,173.41582529323645</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>-34.834723007452865,173.41670830651026</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>-34.83477797908308,173.417588709076</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>-34.83433303607611,173.41836533314213</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-34.829585332276935,173.41117991214873</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-34.830266611879814,173.41089776783332</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-34.8309787730301,173.41085685269906</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-34.83167791739676,173.41111976769886</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-34.83231615099097,173.41152749251444</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-34.8329325683362,173.41196797981326</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-34.83343416723094,173.41260678418004</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-34.83387385515564,173.4133163861666</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-34.83421105812652,173.41410619452103</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>-34.834460396009256,173.4149440489002</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>-34.83459198733941,173.41582617329934</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>-34.83471479342354,173.4167097184829</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>-34.83478086076455,173.4175888915864</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>-34.83434862598945,173.41836996654865</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P570"/>
+  <dimension ref="A1:P576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31230,6 +31230,330 @@
         <v>400.68</v>
       </c>
       <c r="P570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:57+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>373.03</v>
+      </c>
+      <c r="C571" t="n">
+        <v>373.65</v>
+      </c>
+      <c r="D571" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="E571" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="F571" t="n">
+        <v>379.41</v>
+      </c>
+      <c r="G571" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="H571" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="I571" t="n">
+        <v>368.74</v>
+      </c>
+      <c r="J571" t="n">
+        <v>367.35</v>
+      </c>
+      <c r="K571" t="n">
+        <v>364.12</v>
+      </c>
+      <c r="L571" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="M571" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="N571" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="O571" t="n">
+        <v>402.27</v>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="C572" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="D572" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="E572" t="n">
+        <v>370.24</v>
+      </c>
+      <c r="F572" t="n">
+        <v>379</v>
+      </c>
+      <c r="G572" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="H572" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="I572" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="J572" t="n">
+        <v>366.46</v>
+      </c>
+      <c r="K572" t="n">
+        <v>363.93</v>
+      </c>
+      <c r="L572" t="n">
+        <v>368.68</v>
+      </c>
+      <c r="M572" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="N572" t="n">
+        <v>371.09</v>
+      </c>
+      <c r="O572" t="n">
+        <v>402.48</v>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>371.76</v>
+      </c>
+      <c r="C573" t="n">
+        <v>372.27</v>
+      </c>
+      <c r="D573" t="n">
+        <v>363.93</v>
+      </c>
+      <c r="E573" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="F573" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="G573" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="H573" t="n">
+        <v>367.93</v>
+      </c>
+      <c r="I573" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="J573" t="n">
+        <v>365.7</v>
+      </c>
+      <c r="K573" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="L573" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="M573" t="n">
+        <v>367.51</v>
+      </c>
+      <c r="N573" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="O573" t="n">
+        <v>402</v>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="C574" t="n">
+        <v>372.73</v>
+      </c>
+      <c r="D574" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="E574" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="F574" t="n">
+        <v>378.8</v>
+      </c>
+      <c r="G574" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="H574" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="I574" t="n">
+        <v>368.08</v>
+      </c>
+      <c r="J574" t="n">
+        <v>365.41</v>
+      </c>
+      <c r="K574" t="n">
+        <v>363.65</v>
+      </c>
+      <c r="L574" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="M574" t="n">
+        <v>367.8</v>
+      </c>
+      <c r="N574" t="n">
+        <v>370.59</v>
+      </c>
+      <c r="O574" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>370.86</v>
+      </c>
+      <c r="C575" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D575" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="E575" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="F575" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="G575" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="H575" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="I575" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="J575" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="K575" t="n">
+        <v>363.71</v>
+      </c>
+      <c r="L575" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="M575" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="N575" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="O575" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>370.86</v>
+      </c>
+      <c r="C576" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D576" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="E576" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="F576" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="G576" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="H576" t="n">
+        <v>368.64</v>
+      </c>
+      <c r="I576" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="J576" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="K576" t="n">
+        <v>363.71</v>
+      </c>
+      <c r="L576" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="M576" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="N576" t="n">
+        <v>371.14</v>
+      </c>
+      <c r="O576" t="n">
+        <v>402.99</v>
+      </c>
+      <c r="P576" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31246,7 +31570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37689,6 +38013,66 @@
       </c>
       <c r="B644" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -37857,28 +38241,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2941550142986996</v>
+        <v>0.298981685140194</v>
       </c>
       <c r="J2" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K2" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1226638497364279</v>
+        <v>0.1285949996179349</v>
       </c>
       <c r="M2" t="n">
-        <v>4.543597563155107</v>
+        <v>4.523677880210079</v>
       </c>
       <c r="N2" t="n">
-        <v>35.99912086700491</v>
+        <v>35.68856951779473</v>
       </c>
       <c r="O2" t="n">
-        <v>5.999926738469805</v>
+        <v>5.973991087856989</v>
       </c>
       <c r="P2" t="n">
-        <v>361.5585878758817</v>
+        <v>361.5091589840109</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37935,28 +38319,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1830567736580588</v>
+        <v>0.1788986299808836</v>
       </c>
       <c r="J3" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K3" t="n">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.103027810969066</v>
+        <v>0.1007072562095589</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27723361381081</v>
+        <v>3.264999559735517</v>
       </c>
       <c r="N3" t="n">
-        <v>16.99823773602411</v>
+        <v>16.86566013312508</v>
       </c>
       <c r="O3" t="n">
-        <v>4.122891914181611</v>
+        <v>4.106782211552627</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0158949101711</v>
+        <v>370.0584678586422</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38013,28 +38397,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1562358299745437</v>
+        <v>0.1449990620925816</v>
       </c>
       <c r="J4" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K4" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0531028979022562</v>
+        <v>0.04655098843138494</v>
       </c>
       <c r="M4" t="n">
-        <v>4.014684841955741</v>
+        <v>4.032659759820846</v>
       </c>
       <c r="N4" t="n">
-        <v>25.31837292200539</v>
+        <v>25.37131374427009</v>
       </c>
       <c r="O4" t="n">
-        <v>5.031736571205352</v>
+        <v>5.036994515012905</v>
       </c>
       <c r="P4" t="n">
-        <v>365.932587531743</v>
+        <v>366.0477004661947</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38091,28 +38475,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1911967092319349</v>
+        <v>0.1809083831888436</v>
       </c>
       <c r="J5" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K5" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07132105925913068</v>
+        <v>0.06515898241571327</v>
       </c>
       <c r="M5" t="n">
-        <v>4.420293143376207</v>
+        <v>4.422350317600576</v>
       </c>
       <c r="N5" t="n">
-        <v>27.68844639725623</v>
+        <v>27.6646292596586</v>
       </c>
       <c r="O5" t="n">
-        <v>5.261981223575035</v>
+        <v>5.259717602653074</v>
       </c>
       <c r="P5" t="n">
-        <v>370.4000177529395</v>
+        <v>370.5054115788281</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38169,28 +38553,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1923289521050873</v>
+        <v>0.1889911897654198</v>
       </c>
       <c r="J6" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K6" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08246476553434701</v>
+        <v>0.08148946365184173</v>
       </c>
       <c r="M6" t="n">
-        <v>3.791711234797437</v>
+        <v>3.768184327312176</v>
       </c>
       <c r="N6" t="n">
-        <v>23.94052125339507</v>
+        <v>23.71973349040706</v>
       </c>
       <c r="O6" t="n">
-        <v>4.89290519562714</v>
+        <v>4.870290904084381</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2996863708145</v>
+        <v>375.3338849712291</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38247,28 +38631,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2904919174285035</v>
+        <v>0.2821275596186942</v>
       </c>
       <c r="J7" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K7" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1801107154899415</v>
+        <v>0.173837623751169</v>
       </c>
       <c r="M7" t="n">
-        <v>3.575431514450494</v>
+        <v>3.579306491389771</v>
       </c>
       <c r="N7" t="n">
-        <v>22.34465813410229</v>
+        <v>22.28725923799802</v>
       </c>
       <c r="O7" t="n">
-        <v>4.727013659182961</v>
+        <v>4.720938385321082</v>
       </c>
       <c r="P7" t="n">
-        <v>368.6591813365393</v>
+        <v>368.7448672951635</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38325,28 +38709,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.247069043083307</v>
+        <v>0.2466666947466103</v>
       </c>
       <c r="J8" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K8" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1460531730952001</v>
+        <v>0.1485607823823158</v>
       </c>
       <c r="M8" t="n">
-        <v>3.607990356820027</v>
+        <v>3.572963246487852</v>
       </c>
       <c r="N8" t="n">
-        <v>20.76091296784046</v>
+        <v>20.5453954526224</v>
       </c>
       <c r="O8" t="n">
-        <v>4.556414485957183</v>
+        <v>4.532702885985624</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9086775508464</v>
+        <v>361.9127951139351</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38403,28 +38787,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2978648215922265</v>
+        <v>0.2958812658018013</v>
       </c>
       <c r="J9" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K9" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2050269284248342</v>
+        <v>0.2065582339873399</v>
       </c>
       <c r="M9" t="n">
-        <v>3.555711589160965</v>
+        <v>3.526963027771882</v>
       </c>
       <c r="N9" t="n">
-        <v>20.01105068609781</v>
+        <v>19.81305684233496</v>
       </c>
       <c r="O9" t="n">
-        <v>4.473371288647725</v>
+        <v>4.451186004014543</v>
       </c>
       <c r="P9" t="n">
-        <v>361.2056037986019</v>
+        <v>361.2259259804236</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38481,28 +38865,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3082163312041524</v>
+        <v>0.3047219840489166</v>
       </c>
       <c r="J10" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K10" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2061552182341947</v>
+        <v>0.2059615472244973</v>
       </c>
       <c r="M10" t="n">
-        <v>3.448261044185096</v>
+        <v>3.429435540929019</v>
       </c>
       <c r="N10" t="n">
-        <v>21.27857323564442</v>
+        <v>21.09147571767846</v>
       </c>
       <c r="O10" t="n">
-        <v>4.612870390076489</v>
+        <v>4.592545668545764</v>
       </c>
       <c r="P10" t="n">
-        <v>359.5724104800668</v>
+        <v>359.6082178189807</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38559,28 +38943,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2690744342699698</v>
+        <v>0.2659629327038915</v>
       </c>
       <c r="J11" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K11" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1547774778812711</v>
+        <v>0.1546385160719638</v>
       </c>
       <c r="M11" t="n">
-        <v>3.632985489197389</v>
+        <v>3.609252396364373</v>
       </c>
       <c r="N11" t="n">
-        <v>22.9984261076068</v>
+        <v>22.78300541532212</v>
       </c>
       <c r="O11" t="n">
-        <v>4.795667430880378</v>
+        <v>4.77315466073771</v>
       </c>
       <c r="P11" t="n">
-        <v>358.1340214051842</v>
+        <v>358.1658991068303</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38637,28 +39021,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3382949175613453</v>
+        <v>0.3325292828900376</v>
       </c>
       <c r="J12" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K12" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1957789803522999</v>
+        <v>0.1935535878437903</v>
       </c>
       <c r="M12" t="n">
-        <v>3.967835465345224</v>
+        <v>3.955040610949857</v>
       </c>
       <c r="N12" t="n">
-        <v>27.34577606062883</v>
+        <v>27.14426480003021</v>
       </c>
       <c r="O12" t="n">
-        <v>5.229318890699708</v>
+        <v>5.210015815717857</v>
       </c>
       <c r="P12" t="n">
-        <v>362.646968916808</v>
+        <v>362.7060311014556</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38715,28 +39099,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.344613064040842</v>
+        <v>0.3400910408680724</v>
       </c>
       <c r="J13" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K13" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2121225178092476</v>
+        <v>0.211255215330735</v>
       </c>
       <c r="M13" t="n">
-        <v>4.007078336549531</v>
+        <v>3.988998841773665</v>
       </c>
       <c r="N13" t="n">
-        <v>25.65814992883586</v>
+        <v>25.44271468298958</v>
       </c>
       <c r="O13" t="n">
-        <v>5.065387441137733</v>
+        <v>5.044077188444837</v>
       </c>
       <c r="P13" t="n">
-        <v>360.7958261932233</v>
+        <v>360.8421440910803</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38793,28 +39177,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2366685738595347</v>
+        <v>0.2378842235522073</v>
       </c>
       <c r="J14" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K14" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09143188723710272</v>
+        <v>0.09424425767977562</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3966454175869</v>
+        <v>4.356722480992057</v>
       </c>
       <c r="N14" t="n">
-        <v>32.37657789340171</v>
+        <v>32.04287555484192</v>
       </c>
       <c r="O14" t="n">
-        <v>5.690041993992813</v>
+        <v>5.660642680371366</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0207400214246</v>
+        <v>364.0082872391195</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38871,28 +39255,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07788427696453074</v>
+        <v>0.0829739449849968</v>
       </c>
       <c r="J15" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="K15" t="n">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00699522643174233</v>
+        <v>0.008106972435079407</v>
       </c>
       <c r="M15" t="n">
-        <v>5.460453688172776</v>
+        <v>5.430344056314754</v>
       </c>
       <c r="N15" t="n">
-        <v>49.82032961872514</v>
+        <v>49.36477201320414</v>
       </c>
       <c r="O15" t="n">
-        <v>7.058351763600702</v>
+        <v>7.02600683270406</v>
       </c>
       <c r="P15" t="n">
-        <v>397.860635027625</v>
+        <v>397.8082756951283</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38930,7 +39314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P570"/>
+  <dimension ref="A1:P576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85665,6 +86049,498 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:57+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-34.82958178105912,173.41116670816854</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-34.83026642150393,173.4108959231083</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-34.8309781703493,173.4108616087371</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-34.831676891005415,173.41112373263798</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-34.832314738114206,173.41153066875722</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-34.832930447288284,173.41197081429598</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-34.833433256725144,173.41260767969217</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-34.833872784034,173.41331719655716</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-34.83421264596139,173.41410541390283</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>-34.834460656898734,173.41494396211107</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>-34.83458817830578,173.41582705336208</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>-34.834709168599055,173.41671068537707</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>-34.83477815918816,173.41758872048288</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>-34.834334700168,173.41836582771916</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-34.829580271092055,173.4111610938781</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-34.8302654360283,173.4108863739437</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-34.83097915655414,173.41085382612934</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-34.8316775392526,173.41112122846593</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-34.832316493506546,173.4115267225162</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-34.83293275014031,173.4119677368576</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-34.833434937658915,173.41260602643897</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-34.833876685977074,173.41331424442004</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-34.834220083714094,173.41410175732238</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>-34.834462309198834,173.4149434124466</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>-34.83459065860674,173.41582648029797</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>-34.83471041856005,173.4167104705117</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>-34.83477869950345,173.4175887547036</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>-34.834332860908546,173.41836528108138</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:06+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-34.82957822983987,173.41115350418949</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-34.83026487609863,173.41088094828208</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-34.830979786629214,173.41084885390762</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-34.83167791739676,173.41111976769886</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-34.83231859141427,173.41152200627667</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-34.832935355999105,173.4119642544929</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-34.83343598824249,173.41260499315567</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-34.833880740937445,173.41331117651256</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-34.8342264350534,173.4140986348487</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-34.83446500505686,173.4149425156256</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-34.83459110151763,173.4158263779651</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>-34.83470925788198,173.41671067002954</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>-34.83478131102729,173.41758892010364</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>-34.834337064930146,173.41836653053915</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-34.82957904074832,173.41115651927123</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-34.830265391233944,173.41088593989076</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-34.83097896479212,173.41085533941418</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-34.83167699904662,173.41112331527597</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-34.83231734979543,173.41152479752049</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-34.83293359855947,173.41196660306446</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-34.833433186686236,173.41260774857773</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-34.833877833607374,173.41331337614437</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-34.83422885859075,173.41409744337838</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>-34.83446474416738,173.41494260241473</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>-34.834592518832466,173.41582605049987</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>-34.83470666867708,173.41671111510774</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>-34.83478320213076,173.4175890398761</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>-34.83433224782207,173.4183650988688</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-34.82957571322692,173.4111441470397</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-34.830265503219856,173.4108870250231</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-34.830978896305695,173.41085587987308</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-34.83167670193332,173.4111244630215</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-34.83231859141427,173.41152200627667</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-34.83293153811294,173.41196935656203</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-34.83343101548009,173.41260988402968</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-34.83387683899445,173.41331412864994</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-34.834225599350866,173.41409904570054</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>-34.834464222388405,173.41494277599298</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>-34.83458667240875,173.41582740129385</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>-34.83470300807703,173.41671174435626</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>-34.83477932987127,173.41758879462773</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>-34.8343325981572,173.41836520299032</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-34.82957571322692,173.4111441470397</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-34.830265503219856,173.4108870250231</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-34.830978896305695,173.41085587987308</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-34.83167670193332,173.4111244630215</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-34.83231859141427,173.41152200627667</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-34.83293153811294,173.41196935656203</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-34.83343101548009,173.41260988402968</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-34.83387683899445,173.41331412864994</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-34.834225599350866,173.41409904570054</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>-34.834464222388405,173.41494277599298</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>-34.83458667240875,173.41582740129385</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>-34.83470300807703,173.41671174435626</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>-34.83477824924071,173.41758872618632</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>-34.834328394135575,173.4183639535327</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P576"/>
+  <dimension ref="A1:P582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31554,6 +31554,330 @@
         <v>402.99</v>
       </c>
       <c r="P576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>370.86</v>
+      </c>
+      <c r="C577" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D577" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="E577" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="F577" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="G577" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="H577" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="I577" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="J577" t="n">
+        <v>365.58</v>
+      </c>
+      <c r="K577" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="L577" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="M577" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="N577" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="O577" t="n">
+        <v>401.09</v>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>370.86</v>
+      </c>
+      <c r="C578" t="n">
+        <v>372.83</v>
+      </c>
+      <c r="D578" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="E578" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="F578" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="G578" t="n">
+        <v>372.44</v>
+      </c>
+      <c r="H578" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="I578" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="J578" t="n">
+        <v>364.09</v>
+      </c>
+      <c r="K578" t="n">
+        <v>362.46</v>
+      </c>
+      <c r="L578" t="n">
+        <v>367.79</v>
+      </c>
+      <c r="M578" t="n">
+        <v>367.21</v>
+      </c>
+      <c r="N578" t="n">
+        <v>370</v>
+      </c>
+      <c r="O578" t="n">
+        <v>399.52</v>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>370.69</v>
+      </c>
+      <c r="C579" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="D579" t="n">
+        <v>363.88</v>
+      </c>
+      <c r="E579" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="F579" t="n">
+        <v>378.6</v>
+      </c>
+      <c r="G579" t="n">
+        <v>371.8</v>
+      </c>
+      <c r="H579" t="n">
+        <v>366.44</v>
+      </c>
+      <c r="I579" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="J579" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="K579" t="n">
+        <v>361.58</v>
+      </c>
+      <c r="L579" t="n">
+        <v>367.29</v>
+      </c>
+      <c r="M579" t="n">
+        <v>366.39</v>
+      </c>
+      <c r="N579" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="O579" t="n">
+        <v>399.3</v>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="C580" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="D580" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="E580" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="F580" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="G580" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="H580" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="I580" t="n">
+        <v>365.57</v>
+      </c>
+      <c r="J580" t="n">
+        <v>362.83</v>
+      </c>
+      <c r="K580" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="L580" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="M580" t="n">
+        <v>366.77</v>
+      </c>
+      <c r="N580" t="n">
+        <v>369.05</v>
+      </c>
+      <c r="O580" t="n">
+        <v>399.42</v>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="C581" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="D581" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="E581" t="n">
+        <v>370.36</v>
+      </c>
+      <c r="F581" t="n">
+        <v>379.69</v>
+      </c>
+      <c r="G581" t="n">
+        <v>372.59</v>
+      </c>
+      <c r="H581" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="I581" t="n">
+        <v>364.96</v>
+      </c>
+      <c r="J581" t="n">
+        <v>362.39</v>
+      </c>
+      <c r="K581" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="L581" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="M581" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="N581" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="O581" t="n">
+        <v>398.21</v>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="C582" t="n">
+        <v>372.93</v>
+      </c>
+      <c r="D582" t="n">
+        <v>366.08</v>
+      </c>
+      <c r="E582" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="F582" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="G582" t="n">
+        <v>373</v>
+      </c>
+      <c r="H582" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="I582" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="J582" t="n">
+        <v>362.8</v>
+      </c>
+      <c r="K582" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="L582" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="M582" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="N582" t="n">
+        <v>369.16</v>
+      </c>
+      <c r="O582" t="n">
+        <v>397.78</v>
+      </c>
+      <c r="P582" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31570,7 +31894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38073,6 +38397,66 @@
       </c>
       <c r="B650" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>0.89</v>
       </c>
     </row>
   </sheetData>
@@ -38241,28 +38625,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.298981685140194</v>
+        <v>0.3006641902401586</v>
       </c>
       <c r="J2" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K2" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1285949996179349</v>
+        <v>0.1323993222273518</v>
       </c>
       <c r="M2" t="n">
-        <v>4.523677880210079</v>
+        <v>4.488114171127292</v>
       </c>
       <c r="N2" t="n">
-        <v>35.68856951779473</v>
+        <v>35.331798817374</v>
       </c>
       <c r="O2" t="n">
-        <v>5.973991087856989</v>
+        <v>5.944055754901194</v>
       </c>
       <c r="P2" t="n">
-        <v>361.5091589840109</v>
+        <v>361.4918633504546</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38319,28 +38703,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1788986299808836</v>
+        <v>0.1744925284371883</v>
       </c>
       <c r="J3" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K3" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1007072562095589</v>
+        <v>0.09799178328914515</v>
       </c>
       <c r="M3" t="n">
-        <v>3.264999559735517</v>
+        <v>3.254223952769555</v>
       </c>
       <c r="N3" t="n">
-        <v>16.86566013312508</v>
+        <v>16.74306468268509</v>
       </c>
       <c r="O3" t="n">
-        <v>4.106782211552627</v>
+        <v>4.091829014351051</v>
       </c>
       <c r="P3" t="n">
-        <v>370.0584678586422</v>
+        <v>370.1037604333287</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38397,28 +38781,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1449990620925816</v>
+        <v>0.1350672824461377</v>
       </c>
       <c r="J4" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K4" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04655098843138494</v>
+        <v>0.04112375115320632</v>
       </c>
       <c r="M4" t="n">
-        <v>4.032659759820846</v>
+        <v>4.043174336564213</v>
       </c>
       <c r="N4" t="n">
-        <v>25.37131374427009</v>
+        <v>25.37104638910347</v>
       </c>
       <c r="O4" t="n">
-        <v>5.036994515012905</v>
+        <v>5.036967975786968</v>
       </c>
       <c r="P4" t="n">
-        <v>366.0477004661947</v>
+        <v>366.149847271149</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38475,28 +38859,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1809083831888436</v>
+        <v>0.1709688860527979</v>
       </c>
       <c r="J5" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K5" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06515898241571327</v>
+        <v>0.05933625129733644</v>
       </c>
       <c r="M5" t="n">
-        <v>4.422350317600576</v>
+        <v>4.422522680602132</v>
       </c>
       <c r="N5" t="n">
-        <v>27.6646292596586</v>
+        <v>27.6386408781569</v>
       </c>
       <c r="O5" t="n">
-        <v>5.259717602653074</v>
+        <v>5.257246511069924</v>
       </c>
       <c r="P5" t="n">
-        <v>370.5054115788281</v>
+        <v>370.6076462299047</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38553,28 +38937,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1889911897654198</v>
+        <v>0.1861960608102039</v>
       </c>
       <c r="J6" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K6" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08148946365184173</v>
+        <v>0.08088202984842563</v>
       </c>
       <c r="M6" t="n">
-        <v>3.768184327312176</v>
+        <v>3.74246676466977</v>
       </c>
       <c r="N6" t="n">
-        <v>23.71973349040706</v>
+        <v>23.49786527550756</v>
       </c>
       <c r="O6" t="n">
-        <v>4.870290904084381</v>
+        <v>4.84745967239621</v>
       </c>
       <c r="P6" t="n">
-        <v>375.3338849712291</v>
+        <v>375.3626255712412</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38631,28 +39015,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2821275596186942</v>
+        <v>0.2744250695622122</v>
       </c>
       <c r="J7" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K7" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L7" t="n">
-        <v>0.173837623751169</v>
+        <v>0.1681998486252768</v>
       </c>
       <c r="M7" t="n">
-        <v>3.579306491389771</v>
+        <v>3.580083120366865</v>
       </c>
       <c r="N7" t="n">
-        <v>22.28725923799802</v>
+        <v>22.21310026865556</v>
       </c>
       <c r="O7" t="n">
-        <v>4.720938385321082</v>
+        <v>4.713077579316465</v>
       </c>
       <c r="P7" t="n">
-        <v>368.7448672951635</v>
+        <v>368.8240904619072</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38709,28 +39093,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2466666947466103</v>
+        <v>0.2439365246145078</v>
       </c>
       <c r="J8" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K8" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1485607823823158</v>
+        <v>0.1484598266295053</v>
       </c>
       <c r="M8" t="n">
-        <v>3.572963246487852</v>
+        <v>3.548332989962649</v>
       </c>
       <c r="N8" t="n">
-        <v>20.5453954526224</v>
+        <v>20.35720140470087</v>
       </c>
       <c r="O8" t="n">
-        <v>4.532702885985624</v>
+        <v>4.511895544524593</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9127951139351</v>
+        <v>361.9408868030336</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38787,28 +39171,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2958812658018013</v>
+        <v>0.2893107237368382</v>
       </c>
       <c r="J9" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K9" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2065582339873399</v>
+        <v>0.2019389424479796</v>
       </c>
       <c r="M9" t="n">
-        <v>3.526963027771882</v>
+        <v>3.518094214352265</v>
       </c>
       <c r="N9" t="n">
-        <v>19.81305684233496</v>
+        <v>19.72937473948752</v>
       </c>
       <c r="O9" t="n">
-        <v>4.451186004014543</v>
+        <v>4.441776079395215</v>
       </c>
       <c r="P9" t="n">
-        <v>361.2259259804236</v>
+        <v>361.2935266728574</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38865,28 +39249,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3047219840489166</v>
+        <v>0.296119839761832</v>
       </c>
       <c r="J10" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K10" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2059615472244973</v>
+        <v>0.1987914408802293</v>
       </c>
       <c r="M10" t="n">
-        <v>3.429435540929019</v>
+        <v>3.435878986610256</v>
       </c>
       <c r="N10" t="n">
-        <v>21.09147571767846</v>
+        <v>21.07905449155791</v>
       </c>
       <c r="O10" t="n">
-        <v>4.592545668545764</v>
+        <v>4.591193144658359</v>
       </c>
       <c r="P10" t="n">
-        <v>359.6082178189807</v>
+        <v>359.6967184587895</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38943,28 +39327,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2659629327038915</v>
+        <v>0.2599543645678422</v>
       </c>
       <c r="J11" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K11" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1546385160719638</v>
+        <v>0.1510932752899986</v>
       </c>
       <c r="M11" t="n">
-        <v>3.609252396364373</v>
+        <v>3.599195486780949</v>
       </c>
       <c r="N11" t="n">
-        <v>22.78300541532212</v>
+        <v>22.64525846575017</v>
       </c>
       <c r="O11" t="n">
-        <v>4.77315466073771</v>
+        <v>4.75870344377018</v>
       </c>
       <c r="P11" t="n">
-        <v>358.1658991068303</v>
+        <v>358.227711154569</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39021,28 +39405,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3325292828900376</v>
+        <v>0.3248829032312837</v>
       </c>
       <c r="J12" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K12" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1935535878437903</v>
+        <v>0.1889717925119375</v>
       </c>
       <c r="M12" t="n">
-        <v>3.955040610949857</v>
+        <v>3.952152818703795</v>
       </c>
       <c r="N12" t="n">
-        <v>27.14426480003021</v>
+        <v>27.0184796989838</v>
       </c>
       <c r="O12" t="n">
-        <v>5.210015815717857</v>
+        <v>5.197930328408011</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7060311014556</v>
+        <v>362.7846864952929</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39099,28 +39483,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3400910408680724</v>
+        <v>0.3345215662625316</v>
       </c>
       <c r="J13" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K13" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L13" t="n">
-        <v>0.211255215330735</v>
+        <v>0.2089849524901378</v>
       </c>
       <c r="M13" t="n">
-        <v>3.988998841773665</v>
+        <v>3.976568541435269</v>
       </c>
       <c r="N13" t="n">
-        <v>25.44271468298958</v>
+        <v>25.26307364143458</v>
       </c>
       <c r="O13" t="n">
-        <v>5.044077188444837</v>
+        <v>5.026238518159936</v>
       </c>
       <c r="P13" t="n">
-        <v>360.8421440910803</v>
+        <v>360.8994336366023</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39177,28 +39561,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2378842235522073</v>
+        <v>0.2358748714715147</v>
       </c>
       <c r="J14" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K14" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09424425767977562</v>
+        <v>0.09468867863534181</v>
       </c>
       <c r="M14" t="n">
-        <v>4.356722480992057</v>
+        <v>4.32323134464439</v>
       </c>
       <c r="N14" t="n">
-        <v>32.04287555484192</v>
+        <v>31.72717945414474</v>
       </c>
       <c r="O14" t="n">
-        <v>5.660642680371366</v>
+        <v>5.632688474799999</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0082872391195</v>
+        <v>364.0289672157896</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39255,28 +39639,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0829739449849968</v>
+        <v>0.08135981958504573</v>
       </c>
       <c r="J15" t="n">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="K15" t="n">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="L15" t="n">
-        <v>0.008106972435079407</v>
+        <v>0.007971625482793399</v>
       </c>
       <c r="M15" t="n">
-        <v>5.430344056314754</v>
+        <v>5.385894452459564</v>
       </c>
       <c r="N15" t="n">
-        <v>49.36477201320414</v>
+        <v>48.87242537081966</v>
       </c>
       <c r="O15" t="n">
-        <v>7.02600683270406</v>
+        <v>6.990881587526688</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8082756951283</v>
+        <v>397.8249676082985</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -39314,7 +39698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P576"/>
+  <dimension ref="A1:P582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86541,6 +86925,498 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-34.82957571322692,173.4111441470397</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>-34.830265503219856,173.4108870250231</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>-34.830978896305695,173.41085587987308</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-34.83167670193332,173.4111244630215</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-34.83231859141427,173.41152200627667</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-34.83293153811294,173.41196935656203</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-34.833432066063715,173.41260885074647</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>-34.833881506024305,173.41331059766208</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>-34.83422743789644,173.4140981418265</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>-34.834466918246434,173.41494187917192</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>-34.834590747188926,173.4158264598314</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>-34.834706311545375,173.41671117649787</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>-34.834783562340945,173.4175890626899</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>-34.83434503505438,173.41836889930318</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-34.82957571322692,173.4111441470397</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>-34.830265503219856,173.4108870250231</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>-34.830978896305695,173.41085587987308</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-34.83167670193332,173.4111244630215</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-34.83231859141427,173.41152200627667</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-34.83293153811294,173.41196935656203</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-34.83344082092689,173.41260024005223</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>-34.83389114611841,173.41330330414482</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>-34.83423988986402,173.41409202013315</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>-34.83447509278363,173.41493915977864</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>-34.83459854242052,173.41582465877252</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>-34.83471193636983,173.41671020960376</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>-34.83478851523098,173.4175893763797</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>-34.83435878570813,173.41837298607294</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-34.82957523786662,173.4111423795781</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-34.830264484147726,173.410877150319</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-34.83097985511562,173.41084831344875</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-34.83167951100413,173.41111361160895</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-34.832318206084295,173.41152287252476</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-34.832935416600485,173.41196417350767</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-34.833446424038996,173.41259472920697</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>-34.83389917952986,173.41329722621248</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>-34.83425108827753,173.41408651471608</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>-34.834482745541806,173.41493661396322</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>-34.83460297152938,173.41582363544345</t>
+        </is>
+      </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>-34.834719257569894,173.41670895110653</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>-34.83479941158905,173.4175900664974</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>-34.83436071255132,173.41837355874142</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>-34.82957557341507,173.41114362719804</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>-34.83026535763816,173.41088561435106</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>-34.83097852647887,173.410858798351</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>-34.831678619664466,173.41111705484573</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>-34.8323168360221,173.4115259525179</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>-34.83293359855947,173.41196660306446</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-34.83344432287198,173.41259679577402</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>-34.833897037286825,173.41329884699456</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>-34.83425041971554,173.41408684339777</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>-34.834478745236396,173.4149379447304</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>-34.83460119988584,173.4158240447751</t>
+        </is>
+      </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>-34.834715864818655,173.4167095343126</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>-34.834797070222855,173.41758991820763</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>-34.834359661545946,173.4183732463768</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>-34.8295736440113,173.4111364533836</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>-34.83026511126913,173.41088322705997</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>-34.830977964889875,173.41086323011368</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>-34.83167721512902,173.41112248055194</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>-34.83231353930962,173.41153336375098</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>-34.83293062909239,173.41197057134033</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-34.83344418279419,173.4125969335452</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>-34.83390170431624,173.41329531600496</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>-34.83425409680649,173.41408503564858</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>-34.83448048449961,173.414937366136</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>-34.83460252861849,173.41582373777638</t>
+        </is>
+      </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>-34.83471291848204,173.416710040781</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>-34.83480013200942,173.41759011212503</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>-34.834370259183444,173.41837639605387</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>-34.82957070796125,173.41112553671002</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>-34.83026561520574,173.41088811015544</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>-34.83097684171139,173.41087209363891</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>-34.8316756485315,173.411128532301</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>-34.83231358212407,173.41153326750123</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>-34.832928144436174,173.41197389173422</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>-34.83344096100469,173.41260010228112</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>-34.83390002112532,173.41329658947666</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>-34.83425067042628,173.41408672014214</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>-34.83447778864163,173.41493826295735</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>-34.83459792234528,173.41582480203857</t>
+        </is>
+      </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>-34.834709168599055,173.41671068537707</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>-34.83479607964485,173.41758985546966</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>-34.83437402528598,173.41837751536082</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
